--- a/23130064_TruongCaoDoan/Group13_23130064_TruongCaoDoan.xlsx
+++ b/23130064_TruongCaoDoan/Group13_23130064_TruongCaoDoan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\n4k1\test\gh\Tester\23130064_TruongCaoDoan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5729AB16-8877-4CE7-8D51-9C1DF6067D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B7327B-A903-47F7-9CE7-67A727CB3690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="475">
   <si>
     <t>TEST CASE SPECIFICATION</t>
   </si>
@@ -612,9 +612,6 @@
     <t>1. Bảng dữ liệu chỉ hiển thị các đơn hàng đã bị hủy (Cancelled).</t>
   </si>
   <si>
-    <t>Kiểm tra lọc danh sách giao hàng theo Quốc gia / Tỉnh thành</t>
-  </si>
-  <si>
     <t>admin_ord_12</t>
   </si>
   <si>
@@ -1101,11 +1098,6 @@
 2. Click nút [Change status]
 3. Chọn 'Complete'  
 4. Click [Save]</t>
-  </si>
-  <si>
-    <t>Step:
-1. Chọn Country = [United States]
-2. Click nút [Search]</t>
   </si>
   <si>
     <t>1. HIển thị list trạng thái có thể thay đổi gồm "Complete"
@@ -1678,6 +1670,26 @@
   <si>
     <t>Không hiển thị thông báo nhập số giá sản phẩm lớn hơn không.
 Hệ thống thực hiện lưu giá sản phẩm là âm trong đơn hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm tra lọc danh sách giao hàng theo Quốc gia </t>
+  </si>
+  <si>
+    <t>Kiểm tra lọc danh sách giao hàng theo Quốc gia</t>
+  </si>
+  <si>
+    <t>Step:
+1. Chọn Country = [United States of America]
+2. Click nút [Search]</t>
+  </si>
+  <si>
+    <t>Do đơn hàng không đủ nhiều để thực hiện chuyển trang</t>
+  </si>
+  <si>
+    <t>Do chuyển trang kế tiếp không được nên không thể thực hiện được test case này</t>
+  </si>
+  <si>
+    <t>Thực tế hệ thống tiến hành tìm kiếm chứ không thông báo ngày nhận không hợp lệ</t>
   </si>
 </sst>
 </file>
@@ -1943,6 +1955,9 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1952,9 +1967,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2184,14 +2196,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="4" spans="2:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3294,13 +3306,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="4" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -4424,7 +4436,7 @@
       <c r="B2" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="30" t="s">
         <v>57</v>
       </c>
       <c r="D2" s="9" t="s">
@@ -4438,7 +4450,7 @@
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="30"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="9" t="s">
         <v>64</v>
       </c>
@@ -4450,7 +4462,7 @@
     <row r="4" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="31"/>
+      <c r="C4" s="32"/>
       <c r="D4" s="9" t="s">
         <v>67</v>
       </c>
@@ -4462,7 +4474,7 @@
     <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="30" t="s">
         <v>68</v>
       </c>
       <c r="D5" s="9" t="s">
@@ -4476,7 +4488,7 @@
     <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="30"/>
+      <c r="C6" s="31"/>
       <c r="D6" s="9" t="s">
         <v>71</v>
       </c>
@@ -4488,7 +4500,7 @@
     <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="30"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="9" t="s">
         <v>72</v>
       </c>
@@ -4500,7 +4512,7 @@
     <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="31"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="9" t="s">
         <v>73</v>
       </c>
@@ -4512,7 +4524,7 @@
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="30" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="9" t="s">
@@ -4526,7 +4538,7 @@
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="30"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="9" t="s">
         <v>76</v>
       </c>
@@ -4538,7 +4550,7 @@
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="30"/>
+      <c r="C11" s="31"/>
       <c r="D11" s="9" t="s">
         <v>77</v>
       </c>
@@ -4550,7 +4562,7 @@
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="30"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="9" t="s">
         <v>78</v>
       </c>
@@ -4562,7 +4574,7 @@
     <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="30"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="9" t="s">
         <v>79</v>
       </c>
@@ -4574,7 +4586,7 @@
     <row r="14" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
-      <c r="C14" s="30"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="9" t="s">
         <v>80</v>
       </c>
@@ -4586,7 +4598,7 @@
     <row r="15" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
-      <c r="C15" s="30"/>
+      <c r="C15" s="31"/>
       <c r="D15" s="9" t="s">
         <v>81</v>
       </c>
@@ -4598,7 +4610,7 @@
     <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="30"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="9" t="s">
         <v>82</v>
       </c>
@@ -4610,7 +4622,7 @@
     <row r="17" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="30"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="9" t="s">
         <v>83</v>
       </c>
@@ -4622,7 +4634,7 @@
     <row r="18" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="30"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="9" t="s">
         <v>84</v>
       </c>
@@ -4634,7 +4646,7 @@
     <row r="19" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="30"/>
+      <c r="C19" s="31"/>
       <c r="D19" s="9" t="s">
         <v>85</v>
       </c>
@@ -4646,7 +4658,7 @@
     <row r="20" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="30"/>
+      <c r="C20" s="31"/>
       <c r="D20" s="9" t="s">
         <v>86</v>
       </c>
@@ -4658,7 +4670,7 @@
     <row r="21" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="31"/>
+      <c r="C21" s="32"/>
       <c r="D21" s="9" t="s">
         <v>87</v>
       </c>
@@ -4670,7 +4682,7 @@
     <row r="22" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="30" t="s">
         <v>88</v>
       </c>
       <c r="D22" s="9" t="s">
@@ -4684,7 +4696,7 @@
     <row r="23" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="30"/>
+      <c r="C23" s="31"/>
       <c r="D23" s="9" t="s">
         <v>90</v>
       </c>
@@ -4696,7 +4708,7 @@
     <row r="24" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="30"/>
+      <c r="C24" s="31"/>
       <c r="D24" s="9" t="s">
         <v>91</v>
       </c>
@@ -4708,7 +4720,7 @@
     <row r="25" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="31"/>
+      <c r="C25" s="32"/>
       <c r="D25" s="9" t="s">
         <v>92</v>
       </c>
@@ -4720,7 +4732,7 @@
     <row r="26" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="30" t="s">
         <v>93</v>
       </c>
       <c r="D26" s="9" t="s">
@@ -4734,7 +4746,7 @@
     <row r="27" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="30"/>
+      <c r="C27" s="31"/>
       <c r="D27" s="9" t="s">
         <v>95</v>
       </c>
@@ -4746,7 +4758,7 @@
     <row r="28" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="31"/>
+      <c r="C28" s="32"/>
       <c r="D28" s="9" t="s">
         <v>96</v>
       </c>
@@ -4758,7 +4770,7 @@
     <row r="29" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="30" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="9" t="s">
@@ -4772,7 +4784,7 @@
     <row r="30" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="31"/>
+      <c r="C30" s="32"/>
       <c r="D30" s="9" t="s">
         <v>99</v>
       </c>
@@ -4784,7 +4796,7 @@
     <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="30" t="s">
         <v>100</v>
       </c>
       <c r="D31" s="9" t="s">
@@ -4798,7 +4810,7 @@
     <row r="32" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
-      <c r="C32" s="30"/>
+      <c r="C32" s="31"/>
       <c r="D32" s="9" t="s">
         <v>104</v>
       </c>
@@ -4810,7 +4822,7 @@
     <row r="33" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="31"/>
+      <c r="C33" s="32"/>
       <c r="D33" s="9" t="s">
         <v>109</v>
       </c>
@@ -4822,7 +4834,7 @@
     <row r="34" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="30" t="s">
         <v>111</v>
       </c>
       <c r="D34" s="9" t="s">
@@ -4836,7 +4848,7 @@
     <row r="35" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
-      <c r="C35" s="30"/>
+      <c r="C35" s="31"/>
       <c r="D35" s="9" t="s">
         <v>115</v>
       </c>
@@ -4848,7 +4860,7 @@
     <row r="36" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
-      <c r="C36" s="31"/>
+      <c r="C36" s="32"/>
       <c r="D36" s="9" t="s">
         <v>118</v>
       </c>
@@ -4860,7 +4872,7 @@
     <row r="37" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="30" t="s">
         <v>120</v>
       </c>
       <c r="D37" s="9" t="s">
@@ -4874,7 +4886,7 @@
     <row r="38" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
-      <c r="C38" s="30"/>
+      <c r="C38" s="31"/>
       <c r="D38" s="9" t="s">
         <v>125</v>
       </c>
@@ -4886,7 +4898,7 @@
     <row r="39" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
-      <c r="C39" s="31"/>
+      <c r="C39" s="32"/>
       <c r="D39" s="9" t="s">
         <v>127</v>
       </c>
@@ -4898,7 +4910,7 @@
     <row r="40" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="30" t="s">
         <v>130</v>
       </c>
       <c r="D40" s="9" t="s">
@@ -4912,7 +4924,7 @@
     <row r="41" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
-      <c r="C41" s="30"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="9" t="s">
         <v>133</v>
       </c>
@@ -4924,7 +4936,7 @@
     <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="30"/>
+      <c r="C42" s="31"/>
       <c r="D42" s="9" t="s">
         <v>135</v>
       </c>
@@ -4936,7 +4948,7 @@
     <row r="43" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
-      <c r="C43" s="31"/>
+      <c r="C43" s="32"/>
       <c r="D43" s="9" t="s">
         <v>139</v>
       </c>
@@ -4948,7 +4960,7 @@
     <row r="44" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="30" t="s">
         <v>141</v>
       </c>
       <c r="D44" s="9" t="s">
@@ -4962,7 +4974,7 @@
     <row r="45" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="31"/>
+      <c r="C45" s="32"/>
       <c r="D45" s="9" t="s">
         <v>148</v>
       </c>
@@ -4976,7 +4988,7 @@
       <c r="B46" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" s="30" t="s">
         <v>57</v>
       </c>
       <c r="D46" s="9" t="s">
@@ -4990,7 +5002,7 @@
     <row r="47" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
-      <c r="C47" s="31"/>
+      <c r="C47" s="32"/>
       <c r="D47" s="9" t="s">
         <v>158</v>
       </c>
@@ -5002,7 +5014,7 @@
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
-      <c r="C48" s="29" t="s">
+      <c r="C48" s="30" t="s">
         <v>162</v>
       </c>
       <c r="D48" s="9" t="s">
@@ -5016,7 +5028,7 @@
     <row r="49" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
-      <c r="C49" s="30"/>
+      <c r="C49" s="31"/>
       <c r="D49" s="9" t="s">
         <v>174</v>
       </c>
@@ -5028,9 +5040,9 @@
     <row r="50" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
-      <c r="C50" s="30"/>
+      <c r="C50" s="31"/>
       <c r="D50" s="9" t="s">
-        <v>179</v>
+        <v>470</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>70</v>
@@ -5040,9 +5052,9 @@
     <row r="51" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
-      <c r="C51" s="30"/>
+      <c r="C51" s="31"/>
       <c r="D51" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>70</v>
@@ -5052,9 +5064,9 @@
     <row r="52" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
-      <c r="C52" s="30"/>
+      <c r="C52" s="31"/>
       <c r="D52" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>70</v>
@@ -5064,9 +5076,9 @@
     <row r="53" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
-      <c r="C53" s="30"/>
+      <c r="C53" s="31"/>
       <c r="D53" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>70</v>
@@ -5076,9 +5088,9 @@
     <row r="54" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
-      <c r="C54" s="31"/>
+      <c r="C54" s="32"/>
       <c r="D54" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>70</v>
@@ -5088,11 +5100,11 @@
     <row r="55" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
-      <c r="C55" s="29" t="s">
-        <v>197</v>
+      <c r="C55" s="30" t="s">
+        <v>196</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>70</v>
@@ -5102,9 +5114,9 @@
     <row r="56" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
-      <c r="C56" s="31"/>
+      <c r="C56" s="32"/>
       <c r="D56" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E56" s="15" t="s">
         <v>70</v>
@@ -5114,11 +5126,11 @@
     <row r="57" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>206</v>
       </c>
       <c r="E57" s="15" t="s">
         <v>70</v>
@@ -5128,9 +5140,9 @@
     <row r="58" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
-      <c r="C58" s="30"/>
+      <c r="C58" s="31"/>
       <c r="D58" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E58" s="15" t="s">
         <v>70</v>
@@ -5140,9 +5152,9 @@
     <row r="59" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
       <c r="B59" s="9"/>
-      <c r="C59" s="30"/>
+      <c r="C59" s="31"/>
       <c r="D59" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E59" s="15" t="s">
         <v>70</v>
@@ -5152,9 +5164,9 @@
     <row r="60" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
       <c r="B60" s="9"/>
-      <c r="C60" s="30"/>
+      <c r="C60" s="31"/>
       <c r="D60" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E60" s="15" t="s">
         <v>70</v>
@@ -5164,9 +5176,9 @@
     <row r="61" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
       <c r="B61" s="9"/>
-      <c r="C61" s="30"/>
+      <c r="C61" s="31"/>
       <c r="D61" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>70</v>
@@ -5176,9 +5188,9 @@
     <row r="62" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
       <c r="B62" s="9"/>
-      <c r="C62" s="31"/>
+      <c r="C62" s="32"/>
       <c r="D62" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>70</v>
@@ -5188,11 +5200,11 @@
     <row r="63" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
       <c r="B63" s="9"/>
-      <c r="C63" s="29" t="s">
-        <v>220</v>
+      <c r="C63" s="30" t="s">
+        <v>219</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>70</v>
@@ -5202,9 +5214,9 @@
     <row r="64" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
       <c r="B64" s="9"/>
-      <c r="C64" s="30"/>
+      <c r="C64" s="31"/>
       <c r="D64" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E64" s="15" t="s">
         <v>70</v>
@@ -5214,9 +5226,9 @@
     <row r="65" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="9"/>
       <c r="B65" s="9"/>
-      <c r="C65" s="31"/>
+      <c r="C65" s="32"/>
       <c r="D65" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E65" s="15" t="s">
         <v>70</v>
@@ -5226,13 +5238,13 @@
     <row r="66" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
       <c r="B66" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="C66" s="29" t="s">
-        <v>235</v>
+        <v>232</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>234</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>60</v>
@@ -5242,9 +5254,9 @@
     <row r="67" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="9"/>
       <c r="B67" s="9"/>
-      <c r="C67" s="30"/>
+      <c r="C67" s="31"/>
       <c r="D67" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E67" s="15" t="s">
         <v>70</v>
@@ -5254,9 +5266,9 @@
     <row r="68" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="9"/>
       <c r="B68" s="9"/>
-      <c r="C68" s="30"/>
+      <c r="C68" s="31"/>
       <c r="D68" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>70</v>
@@ -5266,9 +5278,9 @@
     <row r="69" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="9"/>
       <c r="B69" s="9"/>
-      <c r="C69" s="30"/>
+      <c r="C69" s="31"/>
       <c r="D69" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E69" s="15" t="s">
         <v>70</v>
@@ -5278,9 +5290,9 @@
     <row r="70" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="9"/>
       <c r="B70" s="9"/>
-      <c r="C70" s="30"/>
+      <c r="C70" s="31"/>
       <c r="D70" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E70" s="15" t="s">
         <v>70</v>
@@ -5290,9 +5302,9 @@
     <row r="71" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
-      <c r="C71" s="31"/>
+      <c r="C71" s="32"/>
       <c r="D71" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E71" s="15" t="s">
         <v>70</v>
@@ -5302,11 +5314,11 @@
     <row r="72" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
-      <c r="C72" s="29" t="s">
-        <v>255</v>
+      <c r="C72" s="30" t="s">
+        <v>254</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E72" s="15" t="s">
         <v>70</v>
@@ -5316,9 +5328,9 @@
     <row r="73" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
-      <c r="C73" s="30"/>
+      <c r="C73" s="31"/>
       <c r="D73" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E73" s="15" t="s">
         <v>70</v>
@@ -5328,9 +5340,9 @@
     <row r="74" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
-      <c r="C74" s="30"/>
+      <c r="C74" s="31"/>
       <c r="D74" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E74" s="15" t="s">
         <v>70</v>
@@ -5340,9 +5352,9 @@
     <row r="75" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
-      <c r="C75" s="30"/>
+      <c r="C75" s="31"/>
       <c r="D75" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E75" s="15" t="s">
         <v>70</v>
@@ -5352,9 +5364,9 @@
     <row r="76" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
       <c r="B76" s="9"/>
-      <c r="C76" s="31"/>
+      <c r="C76" s="32"/>
       <c r="D76" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E76" s="15" t="s">
         <v>70</v>
@@ -5364,11 +5376,11 @@
     <row r="77" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="9"/>
       <c r="B77" s="9"/>
-      <c r="C77" s="29" t="s">
-        <v>272</v>
+      <c r="C77" s="30" t="s">
+        <v>271</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E77" s="15" t="s">
         <v>70</v>
@@ -5378,9 +5390,9 @@
     <row r="78" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="9"/>
       <c r="B78" s="9"/>
-      <c r="C78" s="30"/>
+      <c r="C78" s="31"/>
       <c r="D78" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E78" s="15" t="s">
         <v>70</v>
@@ -5390,9 +5402,9 @@
     <row r="79" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
       <c r="B79" s="9"/>
-      <c r="C79" s="30"/>
+      <c r="C79" s="31"/>
       <c r="D79" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E79" s="15" t="s">
         <v>70</v>
@@ -5402,9 +5414,9 @@
     <row r="80" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="9"/>
       <c r="B80" s="9"/>
-      <c r="C80" s="31"/>
+      <c r="C80" s="32"/>
       <c r="D80" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E80" s="15" t="s">
         <v>70</v>
@@ -5414,11 +5426,11 @@
     <row r="81" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="9"/>
       <c r="B81" s="9"/>
-      <c r="C81" s="29" t="s">
-        <v>290</v>
+      <c r="C81" s="30" t="s">
+        <v>289</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E81" s="15" t="s">
         <v>70</v>
@@ -5428,9 +5440,9 @@
     <row r="82" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="9"/>
       <c r="B82" s="9"/>
-      <c r="C82" s="31"/>
+      <c r="C82" s="32"/>
       <c r="D82" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E82" s="15" t="s">
         <v>70</v>
@@ -5441,10 +5453,10 @@
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
       <c r="C83" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E83" s="15" t="s">
         <v>70</v>
@@ -5455,10 +5467,10 @@
       <c r="A84" s="9"/>
       <c r="B84" s="9"/>
       <c r="C84" s="22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E84" s="15" t="s">
         <v>70</v>
@@ -5469,10 +5481,10 @@
       <c r="A85" s="9"/>
       <c r="B85" s="9"/>
       <c r="C85" s="23" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E85" s="15" t="s">
         <v>70</v>
@@ -6396,6 +6408,16 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="C9:C21"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="C57:C62"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C66:C71"/>
     <mergeCell ref="C72:C76"/>
     <mergeCell ref="C77:C80"/>
     <mergeCell ref="C81:C82"/>
@@ -6406,16 +6428,6 @@
     <mergeCell ref="C46:C47"/>
     <mergeCell ref="C48:C54"/>
     <mergeCell ref="C55:C56"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="C57:C62"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="C66:C71"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="C9:C21"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="C26:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -6485,7 +6497,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="16">
         <f>COUNTIF(F9:F52, "Passed")</f>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B6" s="17">
         <f>COUNTIF(F9:F52, "Failed")</f>
@@ -6497,7 +6509,7 @@
       </c>
       <c r="D6" s="19">
         <f>COUNTIF(F9:F52, "Blocked")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="20">
         <f>COUNTIF(F9:F52, "Skipped")</f>
@@ -6553,7 +6565,7 @@
       <c r="F9" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="27">
         <v>46323</v>
       </c>
       <c r="H9" s="9"/>
@@ -6577,7 +6589,7 @@
       <c r="F10" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="27">
         <v>46324</v>
       </c>
       <c r="H10" s="9"/>
@@ -6601,7 +6613,7 @@
       <c r="F11" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="27">
         <v>46325</v>
       </c>
       <c r="H11" s="9"/>
@@ -6625,7 +6637,7 @@
       <c r="F12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="27">
         <v>46326</v>
       </c>
       <c r="H12" s="9"/>
@@ -6649,11 +6661,11 @@
       <c r="F13" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="27">
         <v>46327</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
@@ -6675,7 +6687,7 @@
       <c r="F14" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="27">
         <v>46328</v>
       </c>
       <c r="H14" s="9"/>
@@ -6699,7 +6711,7 @@
       <c r="F15" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="27">
         <v>46329</v>
       </c>
       <c r="H15" s="9"/>
@@ -6723,7 +6735,7 @@
       <c r="F16" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="27">
         <v>46330</v>
       </c>
       <c r="H16" s="9"/>
@@ -6747,7 +6759,7 @@
       <c r="F17" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="27">
         <v>46331</v>
       </c>
       <c r="H17" s="9"/>
@@ -6771,7 +6783,7 @@
       <c r="F18" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="27">
         <v>46332</v>
       </c>
       <c r="H18" s="9"/>
@@ -6795,23 +6807,23 @@
       <c r="F19" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="27">
         <v>46333</v>
       </c>
       <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>182</v>
-      </c>
       <c r="D20" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>112</v>
@@ -6819,23 +6831,23 @@
       <c r="F20" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="27">
         <v>46334</v>
       </c>
       <c r="H20" s="9"/>
     </row>
     <row r="21" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>112</v>
@@ -6843,23 +6855,23 @@
       <c r="F21" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="27">
         <v>46335</v>
       </c>
       <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>112</v>
@@ -6867,23 +6879,23 @@
       <c r="F22" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="27">
         <v>46336</v>
       </c>
       <c r="H22" s="9"/>
     </row>
     <row r="23" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="C23" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>200</v>
-      </c>
       <c r="D23" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>112</v>
@@ -6891,23 +6903,23 @@
       <c r="F23" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="27">
         <v>46337</v>
       </c>
       <c r="H23" s="9"/>
     </row>
     <row r="24" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>211</v>
-      </c>
       <c r="C24" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>112</v>
@@ -6915,23 +6927,23 @@
       <c r="F24" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="27">
         <v>46338</v>
       </c>
       <c r="H24" s="9"/>
     </row>
     <row r="25" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>216</v>
-      </c>
       <c r="C25" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>218</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>219</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>112</v>
@@ -6939,23 +6951,23 @@
       <c r="F25" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="27">
         <v>46339</v>
       </c>
       <c r="H25" s="9"/>
     </row>
     <row r="26" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>223</v>
-      </c>
       <c r="D26" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>112</v>
@@ -6963,23 +6975,23 @@
       <c r="F26" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G26" s="32">
+      <c r="G26" s="27">
         <v>46340</v>
       </c>
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B27" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>112</v>
@@ -6987,23 +6999,23 @@
       <c r="F27" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="27">
         <v>46341</v>
       </c>
       <c r="H27" s="9"/>
     </row>
     <row r="28" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C28" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>112</v>
@@ -7011,23 +7023,23 @@
       <c r="F28" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="27">
         <v>46342</v>
       </c>
       <c r="H28" s="9"/>
     </row>
     <row r="29" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>112</v>
@@ -7035,23 +7047,23 @@
       <c r="F29" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="27">
         <v>46343</v>
       </c>
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>244</v>
-      </c>
       <c r="C30" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>112</v>
@@ -7059,25 +7071,25 @@
       <c r="F30" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="27">
         <v>46344</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>91</v>
       </c>
       <c r="C31" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>252</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>112</v>
@@ -7085,23 +7097,23 @@
       <c r="F31" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="32">
+      <c r="G31" s="27">
         <v>46345</v>
       </c>
       <c r="H31" s="9"/>
     </row>
     <row r="32" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>92</v>
       </c>
       <c r="C32" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>112</v>
@@ -7109,71 +7121,75 @@
       <c r="F32" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="32">
+      <c r="G32" s="27">
         <v>46346</v>
       </c>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>94</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>260</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>261</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>112</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G33" s="32">
+        <v>63</v>
+      </c>
+      <c r="G33" s="27">
         <v>46347</v>
       </c>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+      <c r="H33" s="9" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>266</v>
-      </c>
       <c r="E34" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G34" s="32">
+        <v>63</v>
+      </c>
+      <c r="G34" s="27">
         <v>46348</v>
       </c>
-      <c r="H34" s="9"/>
+      <c r="H34" s="9" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="35" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>96</v>
       </c>
       <c r="C35" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>270</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>271</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>112</v>
@@ -7181,23 +7197,23 @@
       <c r="F35" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="27">
         <v>46349</v>
       </c>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>98</v>
       </c>
       <c r="C36" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>112</v>
@@ -7205,267 +7221,267 @@
       <c r="F36" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="27">
         <v>46350</v>
       </c>
       <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G37" s="32">
+      <c r="G37" s="27">
         <v>46351</v>
       </c>
       <c r="H37" s="9"/>
     </row>
     <row r="38" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C38" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>289</v>
-      </c>
       <c r="E38" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="27">
         <v>46352</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>104</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="27">
         <v>46353</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>109</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G40" s="32">
+      <c r="G40" s="27">
         <v>46354</v>
       </c>
       <c r="H40" s="9"/>
     </row>
     <row r="41" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>113</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="27">
         <v>46355</v>
       </c>
       <c r="H41" s="9"/>
     </row>
     <row r="42" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>115</v>
       </c>
       <c r="C42" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="D42" s="9" t="s">
-        <v>320</v>
-      </c>
       <c r="E42" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="27">
         <v>46356</v>
       </c>
       <c r="H42" s="9"/>
     </row>
     <row r="43" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G43" s="32">
+      <c r="G43" s="27">
         <v>46357</v>
       </c>
       <c r="H43" s="9"/>
     </row>
     <row r="44" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>122</v>
       </c>
       <c r="C44" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>338</v>
-      </c>
       <c r="E44" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="27">
         <v>46358</v>
       </c>
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>125</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="27">
         <v>46359</v>
       </c>
       <c r="H45" s="9"/>
     </row>
     <row r="46" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>127</v>
       </c>
       <c r="C46" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>356</v>
-      </c>
       <c r="E46" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G46" s="32">
+      <c r="G46" s="27">
         <v>46360</v>
       </c>
       <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>132</v>
       </c>
       <c r="C47" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D47" s="9" t="s">
         <v>364</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>112</v>
@@ -7473,23 +7489,23 @@
       <c r="F47" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G47" s="32">
+      <c r="G47" s="27">
         <v>46361</v>
       </c>
       <c r="H47" s="9"/>
     </row>
     <row r="48" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>133</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>112</v>
@@ -7497,23 +7513,23 @@
       <c r="F48" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="27">
         <v>46362</v>
       </c>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>135</v>
       </c>
       <c r="C49" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>382</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>384</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>112</v>
@@ -7521,23 +7537,23 @@
       <c r="F49" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G49" s="32">
+      <c r="G49" s="27">
         <v>46363</v>
       </c>
       <c r="H49" s="9"/>
     </row>
     <row r="50" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>139</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>112</v>
@@ -7545,61 +7561,61 @@
       <c r="F50" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="27">
         <v>46364</v>
       </c>
       <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>145</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="27">
         <v>46365</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="165.6" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>148</v>
       </c>
       <c r="C52" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>402</v>
-      </c>
       <c r="E52" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G52" s="32">
+      <c r="G52" s="27">
         <v>46366</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -7670,15 +7686,15 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="16">
         <f>COUNTIF(F9:F28, "Passed")</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B6" s="17">
         <f>COUNTIF(F9:F28, "Failed")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="18">
         <f>COUNTBLANK(F9:F28) + COUNTIF(F9:F28, "Untested")</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D6" s="19">
         <f>COUNTIF(F9:F28, "Blocked")</f>
@@ -7721,402 +7737,486 @@
     </row>
     <row r="9" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="F9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="27">
+        <v>46323</v>
+      </c>
       <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>158</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="27">
+        <v>46323</v>
+      </c>
       <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="27">
+        <v>46323</v>
+      </c>
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>174</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="27">
+        <v>46323</v>
+      </c>
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>179</v>
+        <v>469</v>
       </c>
       <c r="C13" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>321</v>
-      </c>
       <c r="E13" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="27">
+        <v>46323</v>
+      </c>
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>137</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="27">
+        <v>46323</v>
+      </c>
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>143</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9"/>
+        <v>276</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="27">
+        <v>46323</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>149</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="27">
+        <v>46323</v>
+      </c>
       <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="27">
+        <v>46323</v>
+      </c>
       <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="27">
+        <v>46323</v>
+      </c>
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>367</v>
-      </c>
       <c r="E19" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="27">
+        <v>46323</v>
+      </c>
       <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+        <v>359</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="27">
+        <v>46323</v>
+      </c>
       <c r="H20" s="9"/>
     </row>
     <row r="21" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>385</v>
-      </c>
       <c r="E21" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+        <v>359</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="27">
+        <v>46323</v>
+      </c>
       <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+        <v>367</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="27">
+        <v>46323</v>
+      </c>
       <c r="H22" s="9"/>
     </row>
     <row r="23" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C23" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>398</v>
-      </c>
       <c r="E23" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+        <v>359</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="27">
+        <v>46323</v>
+      </c>
       <c r="H23" s="9"/>
     </row>
     <row r="24" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="9"/>
+        <v>359</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24" s="27">
+        <v>46323</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>408</v>
-      </c>
       <c r="E25" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+        <v>359</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" s="27">
+        <v>46323</v>
+      </c>
       <c r="H25" s="9"/>
     </row>
     <row r="26" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>411</v>
-      </c>
       <c r="D26" s="9" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+        <v>359</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" s="27">
+        <v>46323</v>
+      </c>
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>417</v>
-      </c>
       <c r="D27" s="9" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+        <v>276</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27" s="27">
+        <v>46323</v>
+      </c>
       <c r="H27" s="9"/>
     </row>
     <row r="28" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>422</v>
-      </c>
       <c r="D28" s="9" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+        <v>359</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28" s="27">
+        <v>46323</v>
+      </c>
       <c r="H28" s="9"/>
     </row>
   </sheetData>
@@ -8146,7 +8246,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G2" s="21" t="s">
         <v>4</v>
@@ -8157,7 +8257,7 @@
         <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -8242,16 +8342,16 @@
     </row>
     <row r="9" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>329</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>119</v>
@@ -8262,19 +8362,19 @@
     </row>
     <row r="10" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -8282,19 +8382,19 @@
     </row>
     <row r="11" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>346</v>
-      </c>
       <c r="E11" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -8302,19 +8402,19 @@
     </row>
     <row r="12" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -8322,19 +8422,19 @@
     </row>
     <row r="13" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
@@ -8342,19 +8442,19 @@
     </row>
     <row r="14" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
@@ -8362,19 +8462,19 @@
     </row>
     <row r="15" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
@@ -8382,19 +8482,19 @@
     </row>
     <row r="16" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -8402,19 +8502,19 @@
     </row>
     <row r="17" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
@@ -8422,19 +8522,19 @@
     </row>
     <row r="18" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>421</v>
-      </c>
       <c r="E18" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
@@ -8442,19 +8542,19 @@
     </row>
     <row r="19" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>426</v>
-      </c>
       <c r="E19" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
@@ -8462,19 +8562,19 @@
     </row>
     <row r="20" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>429</v>
-      </c>
       <c r="E20" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -8482,19 +8582,19 @@
     </row>
     <row r="21" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>432</v>
-      </c>
       <c r="E21" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
@@ -8502,19 +8602,19 @@
     </row>
     <row r="22" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>435</v>
-      </c>
       <c r="E22" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
@@ -8522,19 +8622,19 @@
     </row>
     <row r="23" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>438</v>
-      </c>
       <c r="E23" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
@@ -8542,19 +8642,19 @@
     </row>
     <row r="24" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>441</v>
-      </c>
       <c r="E24" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
@@ -8562,19 +8662,19 @@
     </row>
     <row r="25" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>444</v>
-      </c>
       <c r="E25" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
@@ -8582,19 +8682,19 @@
     </row>
     <row r="26" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>447</v>
-      </c>
       <c r="E26" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -8602,19 +8702,19 @@
     </row>
     <row r="27" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>450</v>
-      </c>
       <c r="E27" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -8622,19 +8722,19 @@
     </row>
     <row r="28" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>453</v>
-      </c>
       <c r="E28" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
@@ -8660,16 +8760,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="27" t="s">
-        <v>454</v>
-      </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
+      <c r="B2" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
     </row>
     <row r="4" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -8704,7 +8804,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>12</v>
@@ -8715,10 +8815,10 @@
     </row>
     <row r="7" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>16</v>
@@ -8732,13 +8832,13 @@
         <v>27</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>460</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>62</v>
@@ -8750,7 +8850,7 @@
         <v>65</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -8762,7 +8862,7 @@
       </c>
       <c r="D11" s="8">
         <f>'Admin - Orders'!A6</f>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E11" s="8">
         <f>'Admin - Orders'!B6</f>
@@ -8774,7 +8874,7 @@
       </c>
       <c r="G11" s="8">
         <f>'Admin - Orders'!D6</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" s="8">
         <f>'Admin - Orders'!E6</f>
@@ -8794,15 +8894,15 @@
       </c>
       <c r="D12" s="8">
         <f>'Admin - Shipments'!A6</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E12" s="8">
         <f>'Admin - Shipments'!B6</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="8">
         <f>'Admin - Shipments'!C6</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G12" s="8">
         <f>'Admin - Shipments'!D6</f>
@@ -8822,7 +8922,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D13" s="8">
         <f>'Admin - Gift cards'!A6</f>
@@ -8851,23 +8951,23 @@
     </row>
     <row r="14" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C14" s="24" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D14" s="13">
         <f t="shared" ref="D14:I14" si="0">SUM(D11:D13)</f>
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E14" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" s="13">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G14" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" s="13">
         <f t="shared" si="0"/>
@@ -8880,26 +8980,26 @@
     </row>
     <row r="16" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C16" s="25" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E16" s="26">
         <f>IF(I14-H14=0, 0, (D14+E14)/(I14-H14)*100)</f>
-        <v>52.380952380952387</v>
+        <v>73.80952380952381</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="17" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C17" s="25" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E17" s="26">
         <f>IF(D14+E14=0, 0, D14/(D14+E14)*100)</f>
-        <v>88.63636363636364</v>
+        <v>88.709677419354833</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="3:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/23130064_TruongCaoDoan/Group13_23130064_TruongCaoDoan.xlsx
+++ b/23130064_TruongCaoDoan/Group13_23130064_TruongCaoDoan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\n4k1\test\gh\Tester\23130064_TruongCaoDoan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B7327B-A903-47F7-9CE7-67A727CB3690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF982EC-322E-4881-A4BB-0A39AF01F5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="477">
   <si>
     <t>TEST CASE SPECIFICATION</t>
   </si>
@@ -144,9 +144,6 @@
     <t>Pre-Condition</t>
   </si>
   <si>
-    <t>Bắt đầu tài liệu, thiết kế Test Design, test case cho chức năng (quản lý đơn hàng, quản lý giao hàng và quản lý gift card)</t>
-  </si>
-  <si>
     <t>Quản lý Đơn hàng (Orders)</t>
   </si>
   <si>
@@ -920,9 +917,6 @@
   </si>
   <si>
     <t>1. Số lượng dòng dữ liệu hiển thị trên bảng cập nhật tương ứng chính xác theo giá trị đã chọn.</t>
-  </si>
-  <si>
-    <t>Ràng buộc dữ liệu</t>
   </si>
   <si>
     <t>admin_ord_28</t>
@@ -1690,6 +1684,21 @@
   </si>
   <si>
     <t>Thực tế hệ thống tiến hành tìm kiếm chứ không thông báo ngày nhận không hợp lệ</t>
+  </si>
+  <si>
+    <t>Thực tế hệ thống không thông báo "giá trị thẻ quà tặng phải lớn hơn 0" 
+Hệ thống lưu thẻ quà tặng</t>
+  </si>
+  <si>
+    <t>Thực tế hệ thống không thông báo "buộc nhập tên người nhận" 
+Hệ thống lưu thẻ quà tặng</t>
+  </si>
+  <si>
+    <t>Thực tế hệ thống không thông báo "bắt buộc nhập email người nhận đối với thẻ ảo" 
+Hệ thống lưu thẻ quà tặng</t>
+  </si>
+  <si>
+    <t>Thực hiện automatio danh sách test case của module quản lý thẻ quà tặng  admin_giftcard</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1967,6 +1976,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2286,19 +2301,19 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="69" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="55.2" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>17</v>
+      <c r="C12" s="8">
+        <v>1.2</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>33</v>
+        <v>476</v>
       </c>
       <c r="G12" s="9"/>
     </row>
@@ -3360,16 +3375,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="41.4" x14ac:dyDescent="0.3">
@@ -3377,16 +3392,16 @@
         <v>2</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
@@ -3394,16 +3409,16 @@
         <v>3</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4411,39 +4426,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="30" t="s">
-        <v>57</v>
-      </c>
       <c r="D2" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>59</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>60</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -4452,10 +4467,10 @@
       <c r="B3" s="9"/>
       <c r="C3" s="31"/>
       <c r="D3" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3" s="9"/>
     </row>
@@ -4464,10 +4479,10 @@
       <c r="B4" s="9"/>
       <c r="C4" s="32"/>
       <c r="D4" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F4" s="9"/>
     </row>
@@ -4475,13 +4490,13 @@
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="15" t="s">
         <v>69</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>70</v>
       </c>
       <c r="F5" s="9"/>
     </row>
@@ -4490,10 +4505,10 @@
       <c r="B6" s="9"/>
       <c r="C6" s="31"/>
       <c r="D6" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6" s="9"/>
     </row>
@@ -4502,10 +4517,10 @@
       <c r="B7" s="9"/>
       <c r="C7" s="31"/>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F7" s="9"/>
     </row>
@@ -4514,10 +4529,10 @@
       <c r="B8" s="9"/>
       <c r="C8" s="32"/>
       <c r="D8" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F8" s="9"/>
     </row>
@@ -4525,13 +4540,13 @@
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>75</v>
-      </c>
       <c r="E9" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F9" s="9"/>
     </row>
@@ -4540,10 +4555,10 @@
       <c r="B10" s="9"/>
       <c r="C10" s="31"/>
       <c r="D10" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F10" s="9"/>
     </row>
@@ -4552,10 +4567,10 @@
       <c r="B11" s="9"/>
       <c r="C11" s="31"/>
       <c r="D11" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F11" s="9"/>
     </row>
@@ -4564,10 +4579,10 @@
       <c r="B12" s="9"/>
       <c r="C12" s="31"/>
       <c r="D12" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F12" s="9"/>
     </row>
@@ -4576,10 +4591,10 @@
       <c r="B13" s="9"/>
       <c r="C13" s="31"/>
       <c r="D13" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F13" s="9"/>
     </row>
@@ -4588,10 +4603,10 @@
       <c r="B14" s="9"/>
       <c r="C14" s="31"/>
       <c r="D14" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F14" s="9"/>
     </row>
@@ -4600,10 +4615,10 @@
       <c r="B15" s="9"/>
       <c r="C15" s="31"/>
       <c r="D15" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F15" s="9"/>
     </row>
@@ -4612,10 +4627,10 @@
       <c r="B16" s="9"/>
       <c r="C16" s="31"/>
       <c r="D16" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F16" s="9"/>
     </row>
@@ -4624,10 +4639,10 @@
       <c r="B17" s="9"/>
       <c r="C17" s="31"/>
       <c r="D17" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17" s="9"/>
     </row>
@@ -4636,10 +4651,10 @@
       <c r="B18" s="9"/>
       <c r="C18" s="31"/>
       <c r="D18" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18" s="9"/>
     </row>
@@ -4648,10 +4663,10 @@
       <c r="B19" s="9"/>
       <c r="C19" s="31"/>
       <c r="D19" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F19" s="9"/>
     </row>
@@ -4660,10 +4675,10 @@
       <c r="B20" s="9"/>
       <c r="C20" s="31"/>
       <c r="D20" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F20" s="9"/>
     </row>
@@ -4672,10 +4687,10 @@
       <c r="B21" s="9"/>
       <c r="C21" s="32"/>
       <c r="D21" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F21" s="9"/>
     </row>
@@ -4683,13 +4698,13 @@
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>89</v>
-      </c>
       <c r="E22" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F22" s="9"/>
     </row>
@@ -4698,10 +4713,10 @@
       <c r="B23" s="9"/>
       <c r="C23" s="31"/>
       <c r="D23" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F23" s="9"/>
     </row>
@@ -4710,10 +4725,10 @@
       <c r="B24" s="9"/>
       <c r="C24" s="31"/>
       <c r="D24" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F24" s="9"/>
     </row>
@@ -4722,10 +4737,10 @@
       <c r="B25" s="9"/>
       <c r="C25" s="32"/>
       <c r="D25" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F25" s="9"/>
     </row>
@@ -4733,13 +4748,13 @@
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>94</v>
-      </c>
       <c r="E26" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F26" s="9"/>
     </row>
@@ -4748,10 +4763,10 @@
       <c r="B27" s="9"/>
       <c r="C27" s="31"/>
       <c r="D27" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F27" s="9"/>
     </row>
@@ -4760,10 +4775,10 @@
       <c r="B28" s="9"/>
       <c r="C28" s="32"/>
       <c r="D28" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F28" s="9"/>
     </row>
@@ -4771,13 +4786,13 @@
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="E29" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F29" s="9"/>
     </row>
@@ -4786,10 +4801,10 @@
       <c r="B30" s="9"/>
       <c r="C30" s="32"/>
       <c r="D30" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F30" s="9"/>
     </row>
@@ -4797,13 +4812,13 @@
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="E31" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F31" s="9"/>
     </row>
@@ -4812,10 +4827,10 @@
       <c r="B32" s="9"/>
       <c r="C32" s="31"/>
       <c r="D32" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F32" s="9"/>
     </row>
@@ -4824,10 +4839,10 @@
       <c r="B33" s="9"/>
       <c r="C33" s="32"/>
       <c r="D33" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F33" s="9"/>
     </row>
@@ -4835,13 +4850,13 @@
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F34" s="9"/>
     </row>
@@ -4850,10 +4865,10 @@
       <c r="B35" s="9"/>
       <c r="C35" s="31"/>
       <c r="D35" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F35" s="9"/>
     </row>
@@ -4862,10 +4877,10 @@
       <c r="B36" s="9"/>
       <c r="C36" s="32"/>
       <c r="D36" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F36" s="9"/>
     </row>
@@ -4873,13 +4888,13 @@
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F37" s="9"/>
     </row>
@@ -4888,10 +4903,10 @@
       <c r="B38" s="9"/>
       <c r="C38" s="31"/>
       <c r="D38" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F38" s="9"/>
     </row>
@@ -4900,10 +4915,10 @@
       <c r="B39" s="9"/>
       <c r="C39" s="32"/>
       <c r="D39" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F39" s="9"/>
     </row>
@@ -4911,13 +4926,13 @@
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F40" s="9"/>
     </row>
@@ -4926,10 +4941,10 @@
       <c r="B41" s="9"/>
       <c r="C41" s="31"/>
       <c r="D41" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F41" s="9"/>
     </row>
@@ -4938,10 +4953,10 @@
       <c r="B42" s="9"/>
       <c r="C42" s="31"/>
       <c r="D42" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F42" s="9"/>
     </row>
@@ -4950,10 +4965,10 @@
       <c r="B43" s="9"/>
       <c r="C43" s="32"/>
       <c r="D43" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F43" s="9"/>
     </row>
@@ -4961,13 +4976,13 @@
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F44" s="9"/>
     </row>
@@ -4976,26 +4991,26 @@
       <c r="B45" s="9"/>
       <c r="C45" s="32"/>
       <c r="D45" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F45" s="9"/>
     </row>
     <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F46" s="9"/>
     </row>
@@ -5004,10 +5019,10 @@
       <c r="B47" s="9"/>
       <c r="C47" s="32"/>
       <c r="D47" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F47" s="9"/>
     </row>
@@ -5015,13 +5030,13 @@
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F48" s="9"/>
     </row>
@@ -5030,10 +5045,10 @@
       <c r="B49" s="9"/>
       <c r="C49" s="31"/>
       <c r="D49" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F49" s="9"/>
     </row>
@@ -5042,10 +5057,10 @@
       <c r="B50" s="9"/>
       <c r="C50" s="31"/>
       <c r="D50" s="9" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F50" s="9"/>
     </row>
@@ -5054,10 +5069,10 @@
       <c r="B51" s="9"/>
       <c r="C51" s="31"/>
       <c r="D51" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F51" s="9"/>
     </row>
@@ -5066,10 +5081,10 @@
       <c r="B52" s="9"/>
       <c r="C52" s="31"/>
       <c r="D52" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F52" s="9"/>
     </row>
@@ -5078,10 +5093,10 @@
       <c r="B53" s="9"/>
       <c r="C53" s="31"/>
       <c r="D53" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F53" s="9"/>
     </row>
@@ -5090,10 +5105,10 @@
       <c r="B54" s="9"/>
       <c r="C54" s="32"/>
       <c r="D54" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F54" s="9"/>
     </row>
@@ -5101,13 +5116,13 @@
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F55" s="9"/>
     </row>
@@ -5116,10 +5131,10 @@
       <c r="B56" s="9"/>
       <c r="C56" s="32"/>
       <c r="D56" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F56" s="9"/>
     </row>
@@ -5127,13 +5142,13 @@
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>205</v>
-      </c>
       <c r="E57" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F57" s="9"/>
     </row>
@@ -5142,10 +5157,10 @@
       <c r="B58" s="9"/>
       <c r="C58" s="31"/>
       <c r="D58" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F58" s="9"/>
     </row>
@@ -5154,10 +5169,10 @@
       <c r="B59" s="9"/>
       <c r="C59" s="31"/>
       <c r="D59" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F59" s="9"/>
     </row>
@@ -5166,10 +5181,10 @@
       <c r="B60" s="9"/>
       <c r="C60" s="31"/>
       <c r="D60" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F60" s="9"/>
     </row>
@@ -5178,10 +5193,10 @@
       <c r="B61" s="9"/>
       <c r="C61" s="31"/>
       <c r="D61" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F61" s="9"/>
     </row>
@@ -5190,10 +5205,10 @@
       <c r="B62" s="9"/>
       <c r="C62" s="32"/>
       <c r="D62" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F62" s="9"/>
     </row>
@@ -5201,13 +5216,13 @@
       <c r="A63" s="9"/>
       <c r="B63" s="9"/>
       <c r="C63" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F63" s="9"/>
     </row>
@@ -5216,10 +5231,10 @@
       <c r="B64" s="9"/>
       <c r="C64" s="31"/>
       <c r="D64" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F64" s="9"/>
     </row>
@@ -5228,26 +5243,26 @@
       <c r="B65" s="9"/>
       <c r="C65" s="32"/>
       <c r="D65" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F65" s="9"/>
     </row>
     <row r="66" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
       <c r="B66" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F66" s="9"/>
     </row>
@@ -5256,10 +5271,10 @@
       <c r="B67" s="9"/>
       <c r="C67" s="31"/>
       <c r="D67" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F67" s="9"/>
     </row>
@@ -5268,10 +5283,10 @@
       <c r="B68" s="9"/>
       <c r="C68" s="31"/>
       <c r="D68" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F68" s="9"/>
     </row>
@@ -5280,10 +5295,10 @@
       <c r="B69" s="9"/>
       <c r="C69" s="31"/>
       <c r="D69" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F69" s="9"/>
     </row>
@@ -5292,10 +5307,10 @@
       <c r="B70" s="9"/>
       <c r="C70" s="31"/>
       <c r="D70" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F70" s="9"/>
     </row>
@@ -5304,10 +5319,10 @@
       <c r="B71" s="9"/>
       <c r="C71" s="32"/>
       <c r="D71" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F71" s="9"/>
     </row>
@@ -5315,111 +5330,109 @@
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F72" s="9"/>
     </row>
     <row r="73" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
-      <c r="C73" s="31"/>
+      <c r="C73" s="33"/>
       <c r="D73" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F73" s="9"/>
     </row>
     <row r="74" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
-      <c r="C74" s="31"/>
+      <c r="C74" s="33"/>
       <c r="D74" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F74" s="9"/>
     </row>
     <row r="75" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
-      <c r="C75" s="31"/>
+      <c r="C75" s="33"/>
       <c r="D75" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F75" s="9"/>
     </row>
     <row r="76" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
       <c r="B76" s="9"/>
-      <c r="C76" s="32"/>
+      <c r="C76" s="33"/>
       <c r="D76" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F76" s="9"/>
     </row>
     <row r="77" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="9"/>
       <c r="B77" s="9"/>
-      <c r="C77" s="30" t="s">
-        <v>271</v>
-      </c>
+      <c r="C77" s="33"/>
       <c r="D77" s="9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F77" s="9"/>
     </row>
     <row r="78" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="9"/>
       <c r="B78" s="9"/>
-      <c r="C78" s="31"/>
+      <c r="C78" s="33"/>
       <c r="D78" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F78" s="9"/>
     </row>
     <row r="79" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
       <c r="B79" s="9"/>
-      <c r="C79" s="31"/>
+      <c r="C79" s="33"/>
       <c r="D79" s="9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F79" s="9"/>
     </row>
     <row r="80" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="9"/>
       <c r="B80" s="9"/>
-      <c r="C80" s="32"/>
+      <c r="C80" s="34"/>
       <c r="D80" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F80" s="9"/>
     </row>
@@ -5427,13 +5440,13 @@
       <c r="A81" s="9"/>
       <c r="B81" s="9"/>
       <c r="C81" s="30" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F81" s="9"/>
     </row>
@@ -5442,10 +5455,10 @@
       <c r="B82" s="9"/>
       <c r="C82" s="32"/>
       <c r="D82" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F82" s="9"/>
     </row>
@@ -5453,13 +5466,13 @@
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
       <c r="C83" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F83" s="9"/>
     </row>
@@ -5467,13 +5480,13 @@
       <c r="A84" s="9"/>
       <c r="B84" s="9"/>
       <c r="C84" s="22" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F84" s="9"/>
     </row>
@@ -5481,13 +5494,13 @@
       <c r="A85" s="9"/>
       <c r="B85" s="9"/>
       <c r="C85" s="23" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F85" s="9"/>
     </row>
@@ -6407,19 +6420,7 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="C9:C21"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="C57:C62"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="C66:C71"/>
-    <mergeCell ref="C72:C76"/>
-    <mergeCell ref="C77:C80"/>
+  <mergeCells count="19">
     <mergeCell ref="C81:C82"/>
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="C37:C39"/>
@@ -6428,6 +6429,17 @@
     <mergeCell ref="C46:C47"/>
     <mergeCell ref="C48:C54"/>
     <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C72:C80"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="C57:C62"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C66:C71"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="C9:C21"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="C26:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -6452,23 +6464,23 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -6476,22 +6488,22 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="E5" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -6522,48 +6534,48 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="C8" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9" s="27">
         <v>46323</v>
@@ -6572,22 +6584,22 @@
     </row>
     <row r="10" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="E10" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10" s="27">
         <v>46324</v>
@@ -6596,22 +6608,22 @@
     </row>
     <row r="11" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>129</v>
-      </c>
       <c r="D11" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11" s="27">
         <v>46325</v>
@@ -6620,22 +6632,22 @@
     </row>
     <row r="12" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>138</v>
-      </c>
       <c r="E12" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12" s="27">
         <v>46326</v>
@@ -6644,48 +6656,48 @@
     </row>
     <row r="13" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>144</v>
-      </c>
       <c r="E13" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13" s="27">
         <v>46327</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>147</v>
-      </c>
       <c r="C14" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>150</v>
-      </c>
       <c r="E14" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14" s="27">
         <v>46328</v>
@@ -6694,22 +6706,22 @@
     </row>
     <row r="15" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>154</v>
-      </c>
       <c r="D15" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G15" s="27">
         <v>46329</v>
@@ -6718,22 +6730,22 @@
     </row>
     <row r="16" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="D16" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>161</v>
-      </c>
       <c r="E16" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16" s="27">
         <v>46330</v>
@@ -6742,22 +6754,22 @@
     </row>
     <row r="17" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>166</v>
-      </c>
       <c r="E17" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G17" s="27">
         <v>46331</v>
@@ -6766,22 +6778,22 @@
     </row>
     <row r="18" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>169</v>
-      </c>
       <c r="D18" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18" s="27">
         <v>46332</v>
@@ -6790,22 +6802,22 @@
     </row>
     <row r="19" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>176</v>
-      </c>
       <c r="D19" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19" s="27">
         <v>46333</v>
@@ -6814,22 +6826,22 @@
     </row>
     <row r="20" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>181</v>
-      </c>
       <c r="D20" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20" s="27">
         <v>46334</v>
@@ -6838,22 +6850,22 @@
     </row>
     <row r="21" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="E21" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" s="27">
         <v>46335</v>
@@ -6862,22 +6874,22 @@
     </row>
     <row r="22" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>195</v>
-      </c>
       <c r="E22" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G22" s="27">
         <v>46336</v>
@@ -6886,22 +6898,22 @@
     </row>
     <row r="23" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="C23" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>199</v>
-      </c>
       <c r="D23" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G23" s="27">
         <v>46337</v>
@@ -6910,22 +6922,22 @@
     </row>
     <row r="24" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>210</v>
-      </c>
       <c r="C24" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>213</v>
-      </c>
       <c r="E24" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G24" s="27">
         <v>46338</v>
@@ -6934,22 +6946,22 @@
     </row>
     <row r="25" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>215</v>
-      </c>
       <c r="C25" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>218</v>
-      </c>
       <c r="E25" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G25" s="27">
         <v>46339</v>
@@ -6958,22 +6970,22 @@
     </row>
     <row r="26" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>222</v>
-      </c>
       <c r="D26" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G26" s="27">
         <v>46340</v>
@@ -6982,22 +6994,22 @@
     </row>
     <row r="27" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B27" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>229</v>
-      </c>
       <c r="E27" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G27" s="27">
         <v>46341</v>
@@ -7006,22 +7018,22 @@
     </row>
     <row r="28" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C28" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>236</v>
-      </c>
       <c r="E28" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G28" s="27">
         <v>46342</v>
@@ -7030,22 +7042,22 @@
     </row>
     <row r="29" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G29" s="27">
         <v>46343</v>
@@ -7054,48 +7066,48 @@
     </row>
     <row r="30" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>243</v>
-      </c>
       <c r="C30" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>246</v>
-      </c>
       <c r="E30" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G30" s="27">
         <v>46344</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C31" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>251</v>
-      </c>
       <c r="E31" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G31" s="27">
         <v>46345</v>
@@ -7104,22 +7116,22 @@
     </row>
     <row r="32" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C32" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>256</v>
-      </c>
       <c r="E32" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G32" s="27">
         <v>46346</v>
@@ -7128,74 +7140,74 @@
     </row>
     <row r="33" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>260</v>
-      </c>
       <c r="E33" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G33" s="27">
         <v>46347</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>265</v>
-      </c>
       <c r="E34" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G34" s="27">
         <v>46348</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C35" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>270</v>
-      </c>
       <c r="E35" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G35" s="27">
         <v>46349</v>
@@ -7204,22 +7216,22 @@
     </row>
     <row r="36" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>274</v>
-      </c>
       <c r="E36" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G36" s="27">
         <v>46350</v>
@@ -7228,22 +7240,22 @@
     </row>
     <row r="37" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C37" s="9" t="s">
+      <c r="D37" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>281</v>
-      </c>
       <c r="E37" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G37" s="27">
         <v>46351</v>
@@ -7252,74 +7264,74 @@
     </row>
     <row r="38" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>287</v>
-      </c>
       <c r="D38" s="9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G38" s="27">
         <v>46352</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C39" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>296</v>
-      </c>
       <c r="E39" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G39" s="27">
         <v>46353</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C40" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>304</v>
-      </c>
       <c r="E40" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G40" s="27">
         <v>46354</v>
@@ -7328,22 +7340,22 @@
     </row>
     <row r="41" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C41" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>310</v>
-      </c>
       <c r="E41" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G41" s="27">
         <v>46355</v>
@@ -7352,22 +7364,22 @@
     </row>
     <row r="42" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G42" s="27">
         <v>46356</v>
@@ -7376,22 +7388,22 @@
     </row>
     <row r="43" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G43" s="27">
         <v>46357</v>
@@ -7400,22 +7412,22 @@
     </row>
     <row r="44" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C44" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="E44" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G44" s="27">
         <v>46358</v>
@@ -7424,22 +7436,22 @@
     </row>
     <row r="45" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G45" s="27">
         <v>46359</v>
@@ -7448,22 +7460,22 @@
     </row>
     <row r="46" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C46" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>354</v>
-      </c>
       <c r="E46" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G46" s="27">
         <v>46360</v>
@@ -7472,22 +7484,22 @@
     </row>
     <row r="47" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C47" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="D47" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>364</v>
-      </c>
       <c r="E47" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G47" s="27">
         <v>46361</v>
@@ -7496,22 +7508,22 @@
     </row>
     <row r="48" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G48" s="27">
         <v>46362</v>
@@ -7520,22 +7532,22 @@
     </row>
     <row r="49" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C49" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="B49" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C49" s="9" t="s">
+      <c r="D49" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>382</v>
-      </c>
       <c r="E49" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G49" s="27">
         <v>46363</v>
@@ -7544,22 +7556,22 @@
     </row>
     <row r="50" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G50" s="27">
         <v>46364</v>
@@ -7568,54 +7580,54 @@
     </row>
     <row r="51" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G51" s="27">
         <v>46365</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="165.6" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C52" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>400</v>
-      </c>
       <c r="E52" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G52" s="27">
         <v>46366</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -7641,23 +7653,23 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -7665,22 +7677,22 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="E5" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -7711,48 +7723,48 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="C8" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9" s="27">
         <v>46323</v>
@@ -7761,22 +7773,22 @@
     </row>
     <row r="10" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>295</v>
-      </c>
       <c r="E10" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10" s="27">
         <v>46323</v>
@@ -7785,22 +7797,22 @@
     </row>
     <row r="11" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>300</v>
-      </c>
       <c r="D11" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11" s="27">
         <v>46323</v>
@@ -7809,22 +7821,22 @@
     </row>
     <row r="12" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>311</v>
-      </c>
       <c r="E12" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12" s="27">
         <v>46323</v>
@@ -7833,22 +7845,22 @@
     </row>
     <row r="13" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>471</v>
-      </c>
       <c r="D13" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13" s="27">
         <v>46323</v>
@@ -7857,22 +7869,22 @@
     </row>
     <row r="14" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14" s="27">
         <v>46323</v>
@@ -7881,48 +7893,48 @@
     </row>
     <row r="15" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G15" s="27">
         <v>46323</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16" s="27">
         <v>46323</v>
@@ -7931,22 +7943,22 @@
     </row>
     <row r="17" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G17" s="27">
         <v>46323</v>
@@ -7955,22 +7967,22 @@
     </row>
     <row r="18" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18" s="27">
         <v>46323</v>
@@ -7979,22 +7991,22 @@
     </row>
     <row r="19" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>365</v>
-      </c>
       <c r="E19" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19" s="27">
         <v>46323</v>
@@ -8003,22 +8015,22 @@
     </row>
     <row r="20" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20" s="27">
         <v>46323</v>
@@ -8027,22 +8039,22 @@
     </row>
     <row r="21" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>383</v>
-      </c>
       <c r="E21" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" s="27">
         <v>46323</v>
@@ -8051,22 +8063,22 @@
     </row>
     <row r="22" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G22" s="27">
         <v>46323</v>
@@ -8075,22 +8087,22 @@
     </row>
     <row r="23" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C23" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>396</v>
-      </c>
       <c r="E23" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G23" s="27">
         <v>46323</v>
@@ -8099,48 +8111,48 @@
     </row>
     <row r="24" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G24" s="27">
         <v>46323</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>406</v>
-      </c>
       <c r="E25" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G25" s="27">
         <v>46323</v>
@@ -8149,22 +8161,22 @@
     </row>
     <row r="26" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>409</v>
-      </c>
       <c r="D26" s="9" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G26" s="27">
         <v>46323</v>
@@ -8173,22 +8185,22 @@
     </row>
     <row r="27" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>415</v>
-      </c>
       <c r="D27" s="9" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G27" s="27">
         <v>46323</v>
@@ -8197,22 +8209,22 @@
     </row>
     <row r="28" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>420</v>
-      </c>
       <c r="D28" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G28" s="27">
         <v>46323</v>
@@ -8237,16 +8249,16 @@
     <col min="5" max="5" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
     <col min="9" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G2" s="21" t="s">
         <v>4</v>
@@ -8254,15 +8266,15 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -8270,36 +8282,36 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="E5" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="16">
         <f>COUNTIF(F9:F28, "Passed")</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B6" s="17">
         <f>COUNTIF(F9:F28, "Failed")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6" s="18">
         <f>COUNTBLANK(F9:F28) + COUNTIF(F9:F28, "Untested")</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D6" s="19">
         <f>COUNTIF(F9:F28, "Blocked")</f>
@@ -8316,428 +8328,516 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="C8" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>327</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+        <v>118</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="27">
+        <v>46324</v>
+      </c>
       <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+        <v>310</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="27">
+        <v>46324</v>
+      </c>
       <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>344</v>
-      </c>
       <c r="E11" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+        <v>310</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="27">
+        <v>46324</v>
+      </c>
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+        <v>310</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="27">
+        <v>46324</v>
+      </c>
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+        <v>310</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="27">
+        <v>46324</v>
+      </c>
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+        <v>310</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="27">
+        <v>46324</v>
+      </c>
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
+        <v>310</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="27">
+        <v>46324</v>
+      </c>
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+        <v>371</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="27">
+        <v>46324</v>
+      </c>
       <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="27">
+        <v>46324</v>
+      </c>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>414</v>
-      </c>
       <c r="B18" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>419</v>
-      </c>
       <c r="E18" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="27">
+        <v>46324</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="E19" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="27">
+        <v>46324</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="B20" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" ht="69" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="D20" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="E20" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="27">
+        <v>46324</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="B21" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>430</v>
-      </c>
       <c r="E21" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="9"/>
+        <v>371</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="27">
+        <v>46324</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>433</v>
-      </c>
       <c r="E22" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+        <v>371</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="27">
+        <v>46324</v>
+      </c>
       <c r="H22" s="9"/>
     </row>
     <row r="23" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>436</v>
-      </c>
       <c r="E23" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+        <v>371</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="27">
+        <v>46324</v>
+      </c>
       <c r="H23" s="9"/>
     </row>
     <row r="24" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>439</v>
-      </c>
       <c r="E24" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+        <v>385</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="27">
+        <v>46324</v>
+      </c>
       <c r="H24" s="9"/>
     </row>
     <row r="25" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>442</v>
-      </c>
       <c r="E25" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+        <v>385</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" s="27">
+        <v>46324</v>
+      </c>
       <c r="H25" s="9"/>
     </row>
     <row r="26" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>445</v>
-      </c>
       <c r="E26" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+        <v>435</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="27">
+        <v>46324</v>
+      </c>
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="E27" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+        <v>385</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" s="27">
+        <v>46324</v>
+      </c>
       <c r="H27" s="9"/>
     </row>
     <row r="28" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>451</v>
-      </c>
       <c r="E28" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+        <v>385</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" s="27">
+        <v>46324</v>
+      </c>
       <c r="H28" s="9"/>
     </row>
   </sheetData>
@@ -8761,7 +8861,7 @@
   <sheetData>
     <row r="2" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B2" s="28" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="29"/>
@@ -8804,7 +8904,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>12</v>
@@ -8815,10 +8915,10 @@
     </row>
     <row r="7" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>16</v>
@@ -8832,25 +8932,25 @@
         <v>27</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="F10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>457</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -8858,7 +8958,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="8">
         <f>'Admin - Orders'!A6</f>
@@ -8890,7 +8990,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D12" s="8">
         <f>'Admin - Shipments'!A6</f>
@@ -8922,19 +9022,19 @@
         <v>3</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D13" s="8">
         <f>'Admin - Gift cards'!A6</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E13" s="8">
         <f>'Admin - Gift cards'!B6</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F13" s="8">
         <f>'Admin - Gift cards'!C6</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G13" s="8">
         <f>'Admin - Gift cards'!D6</f>
@@ -8951,19 +9051,19 @@
     </row>
     <row r="14" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C14" s="24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D14" s="13">
         <f t="shared" ref="D14:I14" si="0">SUM(D11:D13)</f>
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E14" s="13">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F14" s="13">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G14" s="13">
         <f t="shared" si="0"/>
@@ -8980,26 +9080,26 @@
     </row>
     <row r="16" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C16" s="25" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E16" s="26">
         <f>IF(I14-H14=0, 0, (D14+E14)/(I14-H14)*100)</f>
-        <v>73.80952380952381</v>
+        <v>97.61904761904762</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="17" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C17" s="25" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E17" s="26">
         <f>IF(D14+E14=0, 0, D14/(D14+E14)*100)</f>
-        <v>88.709677419354833</v>
+        <v>86.58536585365853</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="21" spans="3:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/23130064_TruongCaoDoan/Group13_23130064_TruongCaoDoan.xlsx
+++ b/23130064_TruongCaoDoan/Group13_23130064_TruongCaoDoan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\n4k1\test\gh\Tester\23130064_TruongCaoDoan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF982EC-322E-4881-A4BB-0A39AF01F5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D72497-E2E3-41EC-817F-F010388137B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Admin - Orders" sheetId="4" r:id="rId4"/>
     <sheet name="Admin - Shipments" sheetId="5" r:id="rId5"/>
     <sheet name="Admin - Gift cards" sheetId="6" r:id="rId6"/>
-    <sheet name="Test Report" sheetId="7" r:id="rId7"/>
+    <sheet name="User - Product Details" sheetId="8" r:id="rId7"/>
+    <sheet name="Test Report" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="701">
   <si>
     <t>TEST CASE SPECIFICATION</t>
   </si>
@@ -1616,9 +1617,6 @@
     <t>TEST REPORT</t>
   </si>
   <si>
-    <t>NOP-SALES_TestReport_v1.0</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -1699,17 +1697,778 @@
   </si>
   <si>
     <t>Thực hiện automatio danh sách test case của module quản lý thẻ quà tặng  admin_giftcard</t>
+  </si>
+  <si>
+    <t>Bắt đầu viết test design và các test case của modul quản lý sales bao gồm các modul nhỏ của nó là quản lý quản lý order, shipments, gift card</t>
+  </si>
+  <si>
+    <t>Product Details &amp; Reviews</t>
+  </si>
+  <si>
+    <t>Thiết kế kịch bản kiểm thử Functional &amp; GUI thuần trang Chi tiết sản phẩm và Đánh giá sản phẩm (phù hợp môi trường Local, không đo hiệu năng)</t>
+  </si>
+  <si>
+    <t>SRS nopCommerce Storefront &amp; Bài giảng Đảm bảo &amp; Kiểm thử phần mềm</t>
+  </si>
+  <si>
+    <t>Admin order, shipments, gift cards</t>
+  </si>
+  <si>
+    <t>Bố cục thông tin</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị tiêu đề sản phẩm</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị mô tả ngắn của sản phẩm</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị mã SKU của sản phẩm</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị mã nhà sản xuất MPN</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị trạng thái tồn kho còn hàng 'In stock'</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị giá bán cơ bản theo định dạng tiền tệ</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị giá cũ gạch ngang khi có chiết khấu</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị điểm đánh giá sao trung bình</t>
+  </si>
+  <si>
+    <t>Kiểm tra click liên kết tên nhà sản xuất chuyển trang danh mục</t>
+  </si>
+  <si>
+    <t>Thư viện hình ảnh</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị ảnh đại diện chính của sản phẩm</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị danh sách các ảnh thu nhỏ</t>
+  </si>
+  <si>
+    <t>Kiểm tra click ảnh thu nhỏ để thay đổi ảnh chính</t>
+  </si>
+  <si>
+    <t>Kiểm tra click ảnh chính để mở modal phóng to ảnh</t>
+  </si>
+  <si>
+    <t>Kiểm tra chuyển ảnh kế tiếp trong modal phóng to</t>
+  </si>
+  <si>
+    <t>Kiểm tra chuyển ảnh trước đó trong modal phóng to</t>
+  </si>
+  <si>
+    <t>Kiểm tra đóng modal phóng to ảnh bằng phím Esc</t>
+  </si>
+  <si>
+    <t>Chọn thuộc tính</t>
+  </si>
+  <si>
+    <t>Kiểm tra chọn thuộc tính kiểu Radio button</t>
+  </si>
+  <si>
+    <t>Kiểm tra chọn thuộc tính kiểu Dropdown list</t>
+  </si>
+  <si>
+    <t>Kiểm tra chọn thuộc tính kiểu Checkbox</t>
+  </si>
+  <si>
+    <t>Tính giá động</t>
+  </si>
+  <si>
+    <t>Kiểm tra đơn giá tự động tăng khi chọn thuộc tính RAM cộng thêm tiền</t>
+  </si>
+  <si>
+    <t>Giá mới = Giá gốc + $60.00</t>
+  </si>
+  <si>
+    <t>Kiểm tra đơn giá tự động tăng khi chọn thuộc tính HDD cộng thêm tiền</t>
+  </si>
+  <si>
+    <t>Giá mới = Giá gốc + $100.00</t>
+  </si>
+  <si>
+    <t>Kiểm tra đơn giá tự động cộng dồn lũy tiến nhiều thuộc tính cùng lúc</t>
+  </si>
+  <si>
+    <t>Cộng dồn đồng thời RAM + HDD + OS</t>
+  </si>
+  <si>
+    <t>Kiểm tra đơn giá tự động trừ bớt khi hủy chọn thuộc tính checkbox</t>
+  </si>
+  <si>
+    <t>Trừ lại đúng số tiền</t>
+  </si>
+  <si>
+    <t>Ràng buộc thuộc tính</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị thông báo lỗi khi chưa chọn thuộc tính bắt buộc</t>
+  </si>
+  <si>
+    <t>Cảnh báo lỗi thuộc tính</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông báo lỗi tự động ẩn sau khi chọn thuộc tính bắt buộc</t>
+  </si>
+  <si>
+    <t>Ẩn thông báo lỗi</t>
+  </si>
+  <si>
+    <t>Hết hàng</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị nhãn 'Out of stock' màu đỏ khi tồn kho bằng 0</t>
+  </si>
+  <si>
+    <t>Kiểm tra vô hiệu hóa các nút tương tác mua khi hết hàng</t>
+  </si>
+  <si>
+    <t>Khóa nút mua hàng</t>
+  </si>
+  <si>
+    <t>Bảng giá sỉ</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị bảng giá mua sỉ theo số lượng</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị đúng các mốc số lượng mua trong bảng giá sỉ</t>
+  </si>
+  <si>
+    <t>Ví dụ: Mua 3+ giá $1,100</t>
+  </si>
+  <si>
+    <t>Tab thông tin</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị nội dung tab mô tả chi tiết</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị bảng thông số kỹ thuật của sản phẩm</t>
+  </si>
+  <si>
+    <t>Điều hướng</t>
+  </si>
+  <si>
+    <t>Kiểm tra phân cấp đường dẫn Breadcrumb trên trang sản phẩm</t>
+  </si>
+  <si>
+    <t>Kiểm tra click liên kết danh mục trên Breadcrumb chuyển đúng trang</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị giao diện chi tiết chuẩn Responsive trên di động</t>
+  </si>
+  <si>
+    <t>Kiểm tra viewport 375x667px</t>
+  </si>
+  <si>
+    <t>Màn hình đánh giá</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị tiêu đề sản phẩm trên trang Product reviews</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị điểm số sao trung bình trên trang đánh giá</t>
+  </si>
+  <si>
+    <t>Danh sách bài viết</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị danh sách các bài đánh giá đã được duyệt</t>
+  </si>
+  <si>
+    <t>Hiển thị tiêu đề, nội dung, người gửi, số sao</t>
+  </si>
+  <si>
+    <t>Kiểm tra bài đánh giá chưa duyệt bị ẩn khỏi danh sách công khai</t>
+  </si>
+  <si>
+    <t>State Transition: Pending ẩn</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị phân trang khi danh sách bài đánh giá vượt quá 1 trang</t>
+  </si>
+  <si>
+    <t>Phân trang danh sách review</t>
+  </si>
+  <si>
+    <t>Bình chọn hữu ích</t>
+  </si>
+  <si>
+    <t>Kiểm tra tăng lượt bình chọn hữu ích khi click [Yes]</t>
+  </si>
+  <si>
+    <t>Helpful count + 1</t>
+  </si>
+  <si>
+    <t>Kiểm tra tăng lượt không hữu ích khi click [No]</t>
+  </si>
+  <si>
+    <t>Not helpful count + 1</t>
+  </si>
+  <si>
+    <t>Kiểm tra chặn bình chọn nhiều lần trên cùng một bài đánh giá</t>
+  </si>
+  <si>
+    <t>Chống spam bình chọn</t>
+  </si>
+  <si>
+    <t>Phân quyền</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị form viết đánh giá khi đã đăng nhập tài khoản</t>
+  </si>
+  <si>
+    <t>Cho phép gửi bài</t>
+  </si>
+  <si>
+    <t>Kiểm tra chặn gửi đánh giá đối với khách vãng lai khi cấu hình bắt buộc đăng nhập</t>
+  </si>
+  <si>
+    <t>Chặn: 'Only registered users can write reviews'</t>
+  </si>
+  <si>
+    <t>Kiểm tra cho phép gửi đánh giá đối với khách vãng lai khi cấu hình mở</t>
+  </si>
+  <si>
+    <t>Cho phép khách vãng lai gửi bài</t>
+  </si>
+  <si>
+    <t>Ràng buộc Tiêu đề</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị lỗi khi để trống trường Tiêu đề</t>
+  </si>
+  <si>
+    <t>Báo lỗi: 'Review title is required.'</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị lỗi khi trường Tiêu đề chỉ chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>Validation chuỗi rỗng</t>
+  </si>
+  <si>
+    <t>Kiểm tra gửi đánh giá với Tiêu đề hợp lệ ngắn nhất 1 ký tự</t>
+  </si>
+  <si>
+    <t>BVA (Biên tối thiểu)</t>
+  </si>
+  <si>
+    <t>Kiểm tra giới hạn độ dài tối đa 200 ký tự của trường Tiêu đề</t>
+  </si>
+  <si>
+    <t>BVA (Biên tối đa)</t>
+  </si>
+  <si>
+    <t>Ràng buộc Nội dung</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị lỗi khi để trống trường Nội dung</t>
+  </si>
+  <si>
+    <t>Báo lỗi: 'Review text is required.'</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị lỗi khi trường Nội dung chỉ chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>Kiểm tra gửi đánh giá với Nội dung hợp lệ thông thường</t>
+  </si>
+  <si>
+    <t>Nội dung hợp lệ</t>
+  </si>
+  <si>
+    <t>Kiểm tra giới hạn độ dài tối đa 1000 ký tự của trường Nội dung</t>
+  </si>
+  <si>
+    <t>Xếp hạng Rating</t>
+  </si>
+  <si>
+    <t>Kiểm tra gửi đánh giá với mức xếp hạng 1 sao</t>
+  </si>
+  <si>
+    <t>Rating = 1 (Bad)</t>
+  </si>
+  <si>
+    <t>Kiểm tra gửi đánh giá với mức xếp hạng 2 sao</t>
+  </si>
+  <si>
+    <t>Rating = 2 (Not good)</t>
+  </si>
+  <si>
+    <t>Kiểm tra gửi đánh giá với mức xếp hạng 3 sao</t>
+  </si>
+  <si>
+    <t>Rating = 3 (Not bad)</t>
+  </si>
+  <si>
+    <t>Kiểm tra gửi đánh giá với mức xếp hạng 4 sao</t>
+  </si>
+  <si>
+    <t>Rating = 4 (Good)</t>
+  </si>
+  <si>
+    <t>Kiểm tra gửi đánh giá với mức xếp hạng 5 sao</t>
+  </si>
+  <si>
+    <t>Rating = 5 (Excellent)</t>
+  </si>
+  <si>
+    <t>Quy trình xử lý</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị thông báo thành công sau khi gửi đánh giá hợp lệ</t>
+  </si>
+  <si>
+    <t>'Product review is successfully added'</t>
+  </si>
+  <si>
+    <t>Kiểm tra các trường nhập liệu tự động làm trống sau khi gửi thành công</t>
+  </si>
+  <si>
+    <t>Reset form</t>
+  </si>
+  <si>
+    <t>Kiểm tra bài đánh giá mới gửi chuyển vào trạng thái chờ duyệt của Admin</t>
+  </si>
+  <si>
+    <t>Kỹ thuật Chuyển đổi trạng thái</t>
+  </si>
+  <si>
+    <t>Kiểm tra điểm sao trung bình tự động cập nhật sau khi Admin duyệt bài</t>
+  </si>
+  <si>
+    <t>Tính lại điểm sao TB</t>
+  </si>
+  <si>
+    <t>2. Chi tiết sản phẩm (Product Details)</t>
+  </si>
+  <si>
+    <t>3. Đánh giá sản phẩm (Product Reviews)</t>
+  </si>
+  <si>
+    <t>2.1 Hiển thị thông tin chung</t>
+  </si>
+  <si>
+    <t>2.2 Thuộc tính sản phẩm</t>
+  </si>
+  <si>
+    <t>2.3 Tồn kho &amp; Giá sỉ</t>
+  </si>
+  <si>
+    <t>4.4 Mô tả &amp; Thông số</t>
+  </si>
+  <si>
+    <t>3.1 Xem danh sách đánh giá</t>
+  </si>
+  <si>
+    <t>3.2 Gửi đánh giá mới</t>
+  </si>
+  <si>
+    <t>Chi tiết sản phẩm (Product Details)</t>
+  </si>
+  <si>
+    <t>Kiểm thử thuần màn hình chi tiết sản phẩm: thông tin sản phẩm, hình ảnh gallery, chọn thuộc tính, tính giá động, bảng giá sỉ, trạng thái tồn kho, bảng thông số kỹ thuật (26 TCs)</t>
+  </si>
+  <si>
+    <t>Truy cập giao diện Storefront khách hàng trên môi trường local</t>
+  </si>
+  <si>
+    <t>Đánh giá sản phẩm (Product Reviews)</t>
+  </si>
+  <si>
+    <t>Kiểm thử màn hình đánh giá sản phẩm: xem danh sách đánh giá, tính điểm sao trung bình, phân quyền gửi bài, validation bắt buộc, BVA ký tự, chọn rating 1-5 sao, bình chọn hữu ích (26 TCs)</t>
+  </si>
+  <si>
+    <t>Truy cập Storefront với tài khoản khách hàng / khách vãng lai</t>
+  </si>
+  <si>
+    <t>User - Product Details</t>
+  </si>
+  <si>
+    <t>User - Product Reviews</t>
+  </si>
+  <si>
+    <t>NOP-SALES_TestReport_v1.3</t>
+  </si>
+  <si>
+    <t>User_ProdDetails</t>
+  </si>
+  <si>
+    <t>Chi tiết sản phẩm bên User (Product Details)</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn A</t>
+  </si>
+  <si>
+    <t>prod_dtl_01</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị đầy đủ tiêu đề, mô tả ngắn, SKU và MPN của sản phẩm</t>
+  </si>
+  <si>
+    <t>Pre-condition:
++ Khách hàng truy cập trang chủ nopCommerce Storefront.
+Step:
+1. Click chọn sản phẩm 'Build your own computer'</t>
+  </si>
+  <si>
+    <t>1. Trang chi tiết sản phẩm hiển thị thành công:
++ Tiêu đề sản phẩm hiển thị 'Build your own computer'
++ Mô tả ngắn hiển thị ngay dưới tiêu đề
++ Mã SKU hiển thị 'COMP_CUST'
++ Mã nhà sản xuất MPN hiển thị chính xác.</t>
+  </si>
+  <si>
+    <t>prod_dtl_02</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị tình trạng còn hàng (Stock availability)</t>
+  </si>
+  <si>
+    <t>Pre-condition:
++ Sản phẩm có số lượng tồn kho &gt; 0.
+Step:
+1. Điều hướng đến trang chi tiết sản phẩm 'Build your own computer'</t>
+  </si>
+  <si>
+    <t>1. Trường Availability hiển thị dòng chữ 'In stock' với nhãn màu xanh lá cây.</t>
+  </si>
+  <si>
+    <t>prod_dtl_03</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị giá bán cơ bản và định dạng tiền tệ</t>
+  </si>
+  <si>
+    <t>Step:
+1. Điều hướng đến trang chi tiết sản phẩm 'Build your own computer'</t>
+  </si>
+  <si>
+    <t>1. Giá bán hiển thị đúng định dạng tiền tệ '$1,200.00' tại khối thông tin giá sản phẩm.</t>
+  </si>
+  <si>
+    <t>prod_dtl_04</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị giá cũ gạch ngang đối với sản phẩm giảm giá</t>
+  </si>
+  <si>
+    <t>Pre-condition:
++ Sản phẩm có cấu hình Old price = $1,500.00 và Price = $1,200.00.
+Step:
+1. Điều hướng đến trang chi tiết sản phẩm giảm giá</t>
+  </si>
+  <si>
+    <t>1. Giá cũ $1,500.00 hiển thị có nét gạch ngang giữa chữ (strikethrough);
++ Giá bán hiện tại $1,200.00 hiển thị nổi bật bên cạnh.</t>
+  </si>
+  <si>
+    <t>prod_dtl_05</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị điểm sao đánh giá trung bình và số lượt review</t>
+  </si>
+  <si>
+    <t>Pre-condition:
++ Sản phẩm đã có bài đánh giá được duyệt trong hệ thống.
+Step:
+1. Điều hướng đến trang chi tiết sản phẩm 'Build your own computer'</t>
+  </si>
+  <si>
+    <t>1. Khối đánh giá sao hiển thị số sao trung bình;
++ Hiển thị liên kết số lượt review (ví dụ: '4 review(s)').</t>
+  </si>
+  <si>
+    <t>prod_dtl_06</t>
+  </si>
+  <si>
+    <t>Step:
+1. Điều hướng đến trang chi tiết sản phẩm
+2. Click vào liên kết tên nhà sản xuất</t>
+  </si>
+  <si>
+    <t>1. Trang chi tiết sản phẩm hiển thị.
+2. Hệ thống điều hướng chính xác sang trang danh mục sản phẩm của nhà sản xuất tương ứng.</t>
+  </si>
+  <si>
+    <t>prod_dtl_07</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị ảnh đại diện chính và các ảnh thu nhỏ</t>
+  </si>
+  <si>
+    <t>1. Ảnh đại diện chính hiển thị rõ ràng tại khung hình ảnh lớn;
++ Danh sách các ảnh thu nhỏ (thumbnails) hiển thị đầy đủ bên dưới.</t>
+  </si>
+  <si>
+    <t>prod_dtl_08</t>
+  </si>
+  <si>
+    <t>Step:
+1. Điều hướng đến trang chi tiết sản phẩm
+2. Click vào ảnh thu nhỏ thứ 2 trong danh sách thumbnails</t>
+  </si>
+  <si>
+    <t>1. Ảnh đại diện chính ban đầu hiển thị góc chụp 1.
+2. Ảnh đại diện chính tự động chuyển sang hiển thị hình ảnh của góc chụp thứ 2 tương ứng.</t>
+  </si>
+  <si>
+    <t>prod_dtl_09</t>
+  </si>
+  <si>
+    <t>Kiểm tra click ảnh chính mở popup phóng to (Lightbox zoom modal)</t>
+  </si>
+  <si>
+    <t>Step:
+1. Click trực tiếp vào ảnh đại diện chính của sản phẩm</t>
+  </si>
+  <si>
+    <t>1. Hộp thoại phóng to ảnh (Lightbox modal) hiển thị với hình ảnh độ phân giải cao và nền tối xung quanh.</t>
+  </si>
+  <si>
+    <t>prod_dtl_10</t>
+  </si>
+  <si>
+    <t>Step:
+1. Click ảnh chính để mở modal phóng to
+2. Click nút mũi tên chuyển tiếp [Next]</t>
+  </si>
+  <si>
+    <t>1. Modal phóng to ảnh hiển thị.
+2. Hình ảnh trong modal chuyển sang góc chụp kế tiếp thành công.</t>
+  </si>
+  <si>
+    <t>prod_dtl_11</t>
+  </si>
+  <si>
+    <t>Step:
+1. Mở modal phóng to và click [Next] chuyển sang ảnh 2
+2. Click nút mũi tên quay lại [Prev]</t>
+  </si>
+  <si>
+    <t>1. Modal hiển thị góc chụp thứ 2.
+2. Hình ảnh trong modal quay trở lại góc chụp ban đầu.</t>
+  </si>
+  <si>
+    <t>prod_dtl_12</t>
+  </si>
+  <si>
+    <t>Kiểm tra đóng popup phóng to ảnh bằng phím Esc</t>
+  </si>
+  <si>
+    <t>Step:
+1. Click ảnh chính để mở modal phóng to
+2. Nhấn phím Esc trên bàn phím</t>
+  </si>
+  <si>
+    <t>1. Modal phóng to ảnh hiển thị.
+2. Modal phóng to được đóng lại mượt mà, màn hình quay về trang chi tiết sản phẩm.</t>
+  </si>
+  <si>
+    <t>prod_dtl_13</t>
+  </si>
+  <si>
+    <t>Kiểm tra chọn thuộc tính sản phẩm dạng nút radio (Processor)</t>
+  </si>
+  <si>
+    <t>Step:
+1. Điều hướng đến trang chi tiết sản phẩm
+2. Click chọn radio button '2.5 GHz Intel Pentium Dual-Core E2200 [+$15.00]'</t>
+  </si>
+  <si>
+    <t>1. Trang chi tiết sản phẩm hiển thị.
+2. Nút radio của tùy chọn được đánh dấu chọn;
++ Các nút radio khác trong nhóm tự động bỏ chọn.</t>
+  </si>
+  <si>
+    <t>prod_dtl_14</t>
+  </si>
+  <si>
+    <t>Kiểm tra chọn thuộc tính sản phẩm dạng danh sách thả xuống (RAM)</t>
+  </si>
+  <si>
+    <t>Step:
+1. Click mở danh sách dropdown tại mục RAM
+2. Click chọn giá trị '8GB [+$60.00]'</t>
+  </si>
+  <si>
+    <t>1. Danh sách các mức dung lượng RAM xổ xuống.
+2. Giá trị '8GB [+$60.00]' được chọn và hiển thị trên khung chọn.</t>
+  </si>
+  <si>
+    <t>prod_dtl_15</t>
+  </si>
+  <si>
+    <t>Kiểm tra chọn thuộc tính sản phẩm dạng ô đánh dấu checkbox (Software)</t>
+  </si>
+  <si>
+    <t>Step:
+1. Tick chọn checkbox 'Microsoft Office [+$50.00]'
+2. Tick chọn tiếp checkbox 'Acrobat Reader [+$10.00]'</t>
+  </si>
+  <si>
+    <t>1. Ô checkbox Microsoft Office hiển thị dấu tích chọn.
+2. Cả hai ô checkbox đều hiển thị tích chọn đồng thời mà không bị loại trừ nhau.</t>
+  </si>
+  <si>
+    <t>prod_dtl_16</t>
+  </si>
+  <si>
+    <t>Step:
+1. Điều hướng đến trang chi tiết sản phẩm
+2. Chọn tùy chọn dropdown RAM: '8GB [+$60.00]'</t>
+  </si>
+  <si>
+    <t>1. Giá sản phẩm ban đầu hiển thị $1,200.00.
+2. Giá sản phẩm tự động cập nhật ngay trên giao diện thành: $1,260.00 ($1,200 + $60).</t>
+  </si>
+  <si>
+    <t>prod_dtl_17</t>
+  </si>
+  <si>
+    <t>Step:
+1. Điều hướng đến trang chi tiết sản phẩm
+2. Click chọn radio button HDD: '400 GB [+$100.00]'</t>
+  </si>
+  <si>
+    <t>1. Giá sản phẩm ban đầu hiển thị $1,200.00.
+2. Giá sản phẩm tự động cập nhật thành $1,300.00 ($1,200 + $100).</t>
+  </si>
+  <si>
+    <t>prod_dtl_18</t>
+  </si>
+  <si>
+    <t>Step:
+1. Chọn RAM: '8GB [+$60.00]'
+2. Chọn HDD: '400 GB [+$100.00]'
+3. Chọn OS: 'Vista Premium [+$60.00]'</t>
+  </si>
+  <si>
+    <t>1. Giá cập nhật thành $1,260.00.
+2. Giá cập nhật thành $1,360.00.
+3. Giá sản phẩm tự động cộng dồn cả 3 thuộc tính thành $1,420.00 ($1,200 + $60 + $100 + $60).</t>
+  </si>
+  <si>
+    <t>prod_dtl_19</t>
+  </si>
+  <si>
+    <t>Pre-condition:
++ Đang tick chọn tùy chọn 'Microsoft Office [+$50.00]' (Giá đang là $1,250.00).
+Step:
+1. Click bỏ dấu tick tại checkbox 'Microsoft Office [+$50.00]'</t>
+  </si>
+  <si>
+    <t>1. Giá sản phẩm ngay lập tức trừ đi $50.00, quay về mức giá gốc $1,200.00.</t>
+  </si>
+  <si>
+    <t>prod_dtl_20</t>
+  </si>
+  <si>
+    <t>Step:
+1. Bỏ trống không chọn thuộc tính Processor
+2. Click nút gửi yêu cầu mua hàng để kích hoạt validation</t>
+  </si>
+  <si>
+    <t>1. Hệ thống hiển thị thanh thông báo lỗi màu đỏ ở đầu trang: 'Please select Processor'.</t>
+  </si>
+  <si>
+    <t>prod_dtl_21</t>
+  </si>
+  <si>
+    <t>Pre-condition:
++ Đang hiển thị thông báo lỗi 'Please select Processor'.
+Step:
+1. Click chọn một tùy chọn Processor bất kỳ</t>
+  </si>
+  <si>
+    <t>1. Thông báo lỗi màu đỏ biến mất ngay lập tức khỏi màn hình.</t>
+  </si>
+  <si>
+    <t>prod_dtl_22</t>
+  </si>
+  <si>
+    <t>Pre-condition:
++ Sản phẩm có số lượng tồn kho = 0 và không cho đặt hàng trước.
+Step:
+1. Điều hướng đến trang chi tiết sản phẩm hết hàng</t>
+  </si>
+  <si>
+    <t>1. Trường Availability hiển thị dòng chữ 'Out of stock' màu đỏ nổi bật.</t>
+  </si>
+  <si>
+    <t>prod_dtl_23</t>
+  </si>
+  <si>
+    <t>Pre-condition:
++ Sản phẩm có số lượng tồn kho = 0.
+Step:
+1. Điều hướng đến trang chi tiết sản phẩm hết hàng</t>
+  </si>
+  <si>
+    <t>1. Các nút tương tác mua hàng bị làm mờ (disabled) hoặc ẩn hoàn toàn.</t>
+  </si>
+  <si>
+    <t>prod_dtl_24</t>
+  </si>
+  <si>
+    <t>Pre-condition:
++ Sản phẩm có cấu hình giá sỉ (Tier prices).
+Step:
+1. Điều hướng đến trang chi tiết sản phẩm có cấu hình giá sỉ</t>
+  </si>
+  <si>
+    <t>1. Bảng Tier prices hiển thị rõ ràng:
++ Hàng số lượng mua tối thiểu ('3+', '5+', '10+')
++ Hàng đơn giá chiết khấu tương ứng ('$1,100.00', '$1,050.00', '$1,000.00').</t>
+  </si>
+  <si>
+    <t>prod_dtl_25</t>
+  </si>
+  <si>
+    <t>Step:
+1. Cuộn chuột xuống khối thông tin chi tiết của sản phẩm</t>
+  </si>
+  <si>
+    <t>1. Tab 'Full description' hiển thị đầy đủ văn bản mô tả, định dạng danh sách và hình ảnh minh họa.</t>
+  </si>
+  <si>
+    <t>prod_dtl_26</t>
+  </si>
+  <si>
+    <t>Step:
+1. Chuyển kích thước màn hình trình duyệt sang tỷ lệ di động (375x667px)</t>
+  </si>
+  <si>
+    <t>1. Giao diện tự động co giãn theo chiều dọc, không tràn chiều ngang;
++ Hình ảnh và các nút chọn thuộc tính hiển thị vừa vặn, thao tác nhạy.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1747,10 +2506,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF385723"/>
@@ -1783,6 +2538,98 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF385723"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFB25900"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1893,44 +2740,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1945,46 +2781,130 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{E8BFD29C-965A-4D2C-8650-4E5275F46F7D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2211,14 +3131,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="4" spans="2:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -2301,12 +3221,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="B12" s="8" t="s">
-        <v>13</v>
+    <row r="12" spans="2:7" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="21">
+        <v>46316</v>
       </c>
       <c r="C12" s="8">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="8" t="s">
@@ -2316,6 +3236,43 @@
         <v>476</v>
       </c>
       <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="2:7" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="B13" s="21">
+        <v>46324</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="105" x14ac:dyDescent="0.3">
+      <c r="B14" s="26">
+        <v>46324</v>
+      </c>
+      <c r="C14" s="24">
+        <v>1.3</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>477</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>478</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3321,13 +4278,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="4" spans="2:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -3414,11 +4371,45 @@
       <c r="D11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="30" t="s">
         <v>51</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="B12" s="47">
+        <v>4</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>607</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>602</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="B13" s="47">
+        <v>5</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>604</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>608</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>605</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4412,2015 +5403,1991 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F147"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="89.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="27" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="9" t="s">
+      <c r="F2" s="30"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="9"/>
+      <c r="F3" s="30"/>
     </row>
     <row r="4" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="9" t="s">
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="30" t="s">
+      <c r="F4" s="30"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="9" t="s">
+      <c r="E5" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="30"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="9" t="s">
+      <c r="E6" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="30"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="30"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="9" t="s">
+      <c r="E7" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="30"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="30" t="s">
+      <c r="E8" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="30"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="9" t="s">
+      <c r="E9" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="30"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="9" t="s">
+      <c r="E10" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="30"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="9" t="s">
+      <c r="E11" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="30"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="9" t="s">
+      <c r="E12" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="30"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="9" t="s">
+      <c r="E13" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="30"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="9" t="s">
+      <c r="E14" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="30"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="9" t="s">
+      <c r="E15" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="30"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="9" t="s">
+      <c r="E16" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="30"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="9" t="s">
+      <c r="E17" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="30"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="30"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="9"/>
-    </row>
-    <row r="19" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="9" t="s">
+      <c r="E18" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="30"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="9" t="s">
+      <c r="E19" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="30"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="9" t="s">
+      <c r="E20" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="30"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="30" t="s">
+      <c r="E21" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="30"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="9" t="s">
+      <c r="E22" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="30"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="9"/>
-    </row>
-    <row r="24" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="9" t="s">
+      <c r="E23" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="30"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="9" t="s">
+      <c r="E24" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="30"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="30"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F25" s="9"/>
-    </row>
-    <row r="26" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="30" t="s">
+      <c r="E25" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="30"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="9" t="s">
+      <c r="E26" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="30"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="30"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="9" t="s">
+      <c r="E27" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" s="30"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="E28" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="30" t="s">
+      <c r="E28" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="30"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="9" t="s">
+      <c r="E29" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="30"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="30"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="30" t="s">
+      <c r="F30" s="30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="30"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="E31" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F31" s="9"/>
-    </row>
-    <row r="32" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="9" t="s">
+      <c r="E31" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" s="30"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="9" t="s">
+      <c r="E32" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" s="30"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="30"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="E33" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="30" t="s">
+      <c r="E33" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="30"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="E34" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="9" t="s">
+      <c r="E34" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="30"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="E35" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F35" s="9"/>
-    </row>
-    <row r="36" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="9" t="s">
+      <c r="E35" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35" s="30"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="E36" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="30" t="s">
+      <c r="E36" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" s="30"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="E37" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F37" s="9"/>
-    </row>
-    <row r="38" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="9" t="s">
+      <c r="E37" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="30"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="E38" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F38" s="9"/>
-    </row>
-    <row r="39" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="9" t="s">
+      <c r="E38" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="30"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="E39" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="30" t="s">
+      <c r="E39" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="30"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="E40" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="9" t="s">
+      <c r="E40" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40" s="30"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F41" s="9"/>
-    </row>
-    <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="9" t="s">
+      <c r="E41" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="30"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="E42" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F42" s="9"/>
-    </row>
-    <row r="43" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="9" t="s">
+      <c r="E42" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F42" s="30"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="E43" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F43" s="9"/>
-    </row>
-    <row r="44" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="30" t="s">
+      <c r="E43" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F43" s="30"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="E44" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F44" s="9"/>
-    </row>
-    <row r="45" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="9" t="s">
+      <c r="E44" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F44" s="30"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="E45" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F45" s="9"/>
-    </row>
-    <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="9"/>
-      <c r="B46" s="11" t="s">
+      <c r="E45" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F45" s="30"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="30"/>
+      <c r="B46" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="C46" s="30" t="s">
+      <c r="C46" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F46" s="9"/>
-    </row>
-    <row r="47" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="9" t="s">
+      <c r="F46" s="30"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="9"/>
-    </row>
-    <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="30" t="s">
+      <c r="F47" s="30"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="E48" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F48" s="9"/>
-    </row>
-    <row r="49" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="9" t="s">
+      <c r="E48" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F48" s="30"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="E49" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F49" s="9"/>
-    </row>
-    <row r="50" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F50" s="9"/>
-    </row>
-    <row r="51" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="9" t="s">
+      <c r="E49" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F49" s="30"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="30"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="E50" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" s="30"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="E51" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F51" s="9"/>
-    </row>
-    <row r="52" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="9" t="s">
+      <c r="E51" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51" s="30"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="30"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="E52" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F52" s="9"/>
-    </row>
-    <row r="53" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="9" t="s">
+      <c r="E52" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52" s="30"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="E53" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F53" s="9"/>
-    </row>
-    <row r="54" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="9" t="s">
+      <c r="E53" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F53" s="30"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="E54" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F54" s="9"/>
-    </row>
-    <row r="55" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="30" t="s">
+      <c r="E54" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F54" s="30"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="E55" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F55" s="9"/>
-    </row>
-    <row r="56" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="9" t="s">
+      <c r="E55" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F55" s="30"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="E56" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F56" s="9"/>
-    </row>
-    <row r="57" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="30" t="s">
+      <c r="E56" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56" s="30"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="E57" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F57" s="9"/>
-    </row>
-    <row r="58" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="9" t="s">
+      <c r="E57" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F57" s="30"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="30"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="E58" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F58" s="9"/>
-    </row>
-    <row r="59" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="9" t="s">
+      <c r="E58" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F58" s="30"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="E59" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F59" s="9"/>
-    </row>
-    <row r="60" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="9" t="s">
+      <c r="E59" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F59" s="30"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="30"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="E60" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F60" s="9"/>
-    </row>
-    <row r="61" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="9" t="s">
+      <c r="E60" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F60" s="30"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="E61" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F61" s="9"/>
-    </row>
-    <row r="62" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="9"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="9" t="s">
+      <c r="E61" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61" s="30"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="E62" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F62" s="9"/>
-    </row>
-    <row r="63" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="9"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="30" t="s">
+      <c r="E62" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F62" s="30"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="D63" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="E63" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F63" s="9"/>
-    </row>
-    <row r="64" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="9" t="s">
+      <c r="E63" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F63" s="30"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="30"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="E64" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F64" s="9"/>
-    </row>
-    <row r="65" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="32"/>
-      <c r="D65" s="9" t="s">
+      <c r="E64" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F64" s="30"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="E65" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F65" s="9"/>
-    </row>
-    <row r="66" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="9"/>
-      <c r="B66" s="11" t="s">
+      <c r="E65" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F65" s="30"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="30"/>
+      <c r="B66" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="C66" s="30" t="s">
+      <c r="C66" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="D66" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E66" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F66" s="9"/>
-    </row>
-    <row r="67" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="9"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="9" t="s">
+      <c r="F66" s="30"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="30"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="E67" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F67" s="9"/>
-    </row>
-    <row r="68" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="31"/>
-      <c r="D68" s="9" t="s">
+      <c r="E67" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F67" s="30"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="30"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="E68" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F68" s="9"/>
-    </row>
-    <row r="69" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="9"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="9" t="s">
+      <c r="E68" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F68" s="30"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="30"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="E69" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F69" s="9"/>
-    </row>
-    <row r="70" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="9"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="9" t="s">
+      <c r="E69" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F69" s="30"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="30"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="E70" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F70" s="9"/>
-    </row>
-    <row r="71" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="9"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="9" t="s">
+      <c r="E70" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F70" s="30"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="E71" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F71" s="9"/>
-    </row>
-    <row r="72" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="30" t="s">
+      <c r="E71" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F71" s="30"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="30"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="D72" s="9" t="s">
+      <c r="D72" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="E72" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F72" s="9"/>
-    </row>
-    <row r="73" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="33"/>
-      <c r="D73" s="9" t="s">
+      <c r="E72" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F72" s="30"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="30"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="30" t="s">
         <v>260</v>
       </c>
-      <c r="E73" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F73" s="9"/>
-    </row>
-    <row r="74" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="33"/>
-      <c r="D74" s="9" t="s">
+      <c r="E73" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F73" s="30"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="30"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="35"/>
+      <c r="D74" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="E74" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F74" s="9"/>
-    </row>
-    <row r="75" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="9"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="33"/>
-      <c r="D75" s="9" t="s">
+      <c r="E74" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F74" s="30"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="30"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="35"/>
+      <c r="D75" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="E75" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F75" s="9"/>
-    </row>
-    <row r="76" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="9"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="33"/>
-      <c r="D76" s="9" t="s">
+      <c r="E75" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F75" s="30"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="30"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="30" t="s">
         <v>267</v>
       </c>
-      <c r="E76" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F76" s="9"/>
-    </row>
-    <row r="77" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="9"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="33"/>
-      <c r="D77" s="9" t="s">
+      <c r="E76" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F76" s="30"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="30" t="s">
         <v>273</v>
       </c>
-      <c r="E77" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F77" s="9"/>
-    </row>
-    <row r="78" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="9"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="33"/>
-      <c r="D78" s="9" t="s">
+      <c r="E77" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F77" s="30"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="30"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="35"/>
+      <c r="D78" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="E78" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F78" s="9"/>
-    </row>
-    <row r="79" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A79" s="9"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="33"/>
-      <c r="D79" s="9" t="s">
+      <c r="E78" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F78" s="30"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="30"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="35"/>
+      <c r="D79" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="E79" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F79" s="9"/>
-    </row>
-    <row r="80" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="34"/>
-      <c r="D80" s="9" t="s">
+      <c r="E79" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F79" s="30"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="30"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="E80" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F80" s="9"/>
-    </row>
-    <row r="81" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="30" t="s">
+      <c r="E80" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F80" s="30"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="30"/>
+      <c r="B81" s="30"/>
+      <c r="C81" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="D81" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="E81" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F81" s="9"/>
-    </row>
-    <row r="82" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="32"/>
-      <c r="D82" s="9" t="s">
+      <c r="E81" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F81" s="30"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="30"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="33"/>
+      <c r="D82" s="30" t="s">
         <v>295</v>
       </c>
-      <c r="E82" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F82" s="9"/>
-    </row>
-    <row r="83" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="12" t="s">
+      <c r="E82" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F82" s="30"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="D83" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="E83" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F83" s="9"/>
-    </row>
-    <row r="84" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="22" t="s">
+      <c r="E83" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F83" s="30"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="30"/>
+      <c r="B84" s="30"/>
+      <c r="C84" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="D84" s="9" t="s">
+      <c r="D84" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="E84" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F84" s="9"/>
-    </row>
-    <row r="85" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A85" s="9"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="23" t="s">
+      <c r="E84" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F84" s="30"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="30"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="39" t="s">
         <v>318</v>
       </c>
-      <c r="D85" s="9" t="s">
+      <c r="D85" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="E85" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F85" s="9"/>
-    </row>
-    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="E85" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F85" s="30"/>
+    </row>
+    <row r="86" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A86" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B86" s="40" t="s">
+        <v>595</v>
+      </c>
+      <c r="C86" s="41" t="s">
+        <v>481</v>
+      </c>
+      <c r="D86" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="E86" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F86" s="42"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="42"/>
+      <c r="B87" s="42"/>
+      <c r="C87" s="44"/>
+      <c r="D87" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="E87" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F87" s="42"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="42"/>
+      <c r="B88" s="42"/>
+      <c r="C88" s="44"/>
+      <c r="D88" s="42" t="s">
+        <v>484</v>
+      </c>
+      <c r="E88" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F88" s="42"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="42"/>
+      <c r="B89" s="42"/>
+      <c r="C89" s="44"/>
+      <c r="D89" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="E89" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F89" s="42"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="42"/>
+      <c r="B90" s="42"/>
+      <c r="C90" s="44"/>
+      <c r="D90" s="42" t="s">
+        <v>486</v>
+      </c>
+      <c r="E90" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F90" s="42"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="42"/>
+      <c r="B91" s="42"/>
+      <c r="C91" s="44"/>
+      <c r="D91" s="42" t="s">
+        <v>487</v>
+      </c>
+      <c r="E91" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F91" s="42"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="42"/>
+      <c r="B92" s="42"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="E92" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F92" s="42"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="42"/>
+      <c r="B93" s="42"/>
+      <c r="C93" s="44"/>
+      <c r="D93" s="42" t="s">
+        <v>489</v>
+      </c>
+      <c r="E93" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F93" s="42"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="42"/>
+      <c r="B94" s="42"/>
+      <c r="C94" s="45"/>
+      <c r="D94" s="42" t="s">
+        <v>490</v>
+      </c>
+      <c r="E94" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F94" s="42"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="42"/>
+      <c r="B95" s="42"/>
+      <c r="C95" s="41" t="s">
+        <v>491</v>
+      </c>
+      <c r="D95" s="42" t="s">
+        <v>492</v>
+      </c>
+      <c r="E95" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F95" s="42"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="42"/>
+      <c r="B96" s="42"/>
+      <c r="C96" s="44"/>
+      <c r="D96" s="42" t="s">
+        <v>493</v>
+      </c>
+      <c r="E96" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F96" s="42"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="42"/>
+      <c r="B97" s="42"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="42" t="s">
+        <v>494</v>
+      </c>
+      <c r="E97" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F97" s="42"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="42"/>
+      <c r="B98" s="42"/>
+      <c r="C98" s="44"/>
+      <c r="D98" s="42" t="s">
+        <v>495</v>
+      </c>
+      <c r="E98" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F98" s="42"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="42"/>
+      <c r="B99" s="42"/>
+      <c r="C99" s="44"/>
+      <c r="D99" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="E99" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F99" s="42"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="42"/>
+      <c r="B100" s="42"/>
+      <c r="C100" s="44"/>
+      <c r="D100" s="42" t="s">
+        <v>497</v>
+      </c>
+      <c r="E100" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F100" s="42"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="42"/>
+      <c r="B101" s="42"/>
+      <c r="C101" s="45"/>
+      <c r="D101" s="42" t="s">
+        <v>498</v>
+      </c>
+      <c r="E101" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F101" s="42"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="42"/>
+      <c r="B102" s="40" t="s">
+        <v>596</v>
+      </c>
+      <c r="C102" s="41" t="s">
+        <v>499</v>
+      </c>
+      <c r="D102" s="42" t="s">
+        <v>500</v>
+      </c>
+      <c r="E102" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F102" s="42"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="42"/>
+      <c r="B103" s="42"/>
+      <c r="C103" s="44"/>
+      <c r="D103" s="42" t="s">
+        <v>501</v>
+      </c>
+      <c r="E103" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F103" s="42"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="42"/>
+      <c r="B104" s="42"/>
+      <c r="C104" s="45"/>
+      <c r="D104" s="42" t="s">
+        <v>502</v>
+      </c>
+      <c r="E104" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F104" s="42"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="42"/>
+      <c r="B105" s="42"/>
+      <c r="C105" s="41" t="s">
+        <v>503</v>
+      </c>
+      <c r="D105" s="42" t="s">
+        <v>504</v>
+      </c>
+      <c r="E105" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F105" s="42" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="42"/>
+      <c r="B106" s="42"/>
+      <c r="C106" s="44"/>
+      <c r="D106" s="42" t="s">
+        <v>506</v>
+      </c>
+      <c r="E106" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F106" s="42" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="42"/>
+      <c r="B107" s="42"/>
+      <c r="C107" s="44"/>
+      <c r="D107" s="42" t="s">
+        <v>508</v>
+      </c>
+      <c r="E107" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F107" s="42" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="42"/>
+      <c r="B108" s="42"/>
+      <c r="C108" s="45"/>
+      <c r="D108" s="42" t="s">
+        <v>510</v>
+      </c>
+      <c r="E108" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F108" s="42" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="42"/>
+      <c r="B109" s="42"/>
+      <c r="C109" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="D109" s="42" t="s">
+        <v>513</v>
+      </c>
+      <c r="E109" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F109" s="42" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="42"/>
+      <c r="B110" s="42"/>
+      <c r="C110" s="45"/>
+      <c r="D110" s="42" t="s">
+        <v>515</v>
+      </c>
+      <c r="E110" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F110" s="42" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="42"/>
+      <c r="B111" s="40" t="s">
+        <v>597</v>
+      </c>
+      <c r="C111" s="41" t="s">
+        <v>517</v>
+      </c>
+      <c r="D111" s="42" t="s">
+        <v>518</v>
+      </c>
+      <c r="E111" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F111" s="42"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="42"/>
+      <c r="B112" s="42"/>
+      <c r="C112" s="45"/>
+      <c r="D112" s="42" t="s">
+        <v>519</v>
+      </c>
+      <c r="E112" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F112" s="42" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="42"/>
+      <c r="B113" s="42"/>
+      <c r="C113" s="41" t="s">
+        <v>521</v>
+      </c>
+      <c r="D113" s="42" t="s">
+        <v>522</v>
+      </c>
+      <c r="E113" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F113" s="42"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="42"/>
+      <c r="B114" s="42"/>
+      <c r="C114" s="45"/>
+      <c r="D114" s="42" t="s">
+        <v>523</v>
+      </c>
+      <c r="E114" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F114" s="42" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="42"/>
+      <c r="B115" s="40" t="s">
+        <v>598</v>
+      </c>
+      <c r="C115" s="41" t="s">
+        <v>525</v>
+      </c>
+      <c r="D115" s="42" t="s">
+        <v>526</v>
+      </c>
+      <c r="E115" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F115" s="42"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="42"/>
+      <c r="B116" s="42"/>
+      <c r="C116" s="45"/>
+      <c r="D116" s="42" t="s">
+        <v>527</v>
+      </c>
+      <c r="E116" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F116" s="42"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="42"/>
+      <c r="B117" s="42"/>
+      <c r="C117" s="41" t="s">
+        <v>528</v>
+      </c>
+      <c r="D117" s="42" t="s">
+        <v>529</v>
+      </c>
+      <c r="E117" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F117" s="42"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="42"/>
+      <c r="B118" s="42"/>
+      <c r="C118" s="44"/>
+      <c r="D118" s="42" t="s">
+        <v>530</v>
+      </c>
+      <c r="E118" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F118" s="42"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="42"/>
+      <c r="B119" s="42"/>
+      <c r="C119" s="45"/>
+      <c r="D119" s="42" t="s">
+        <v>531</v>
+      </c>
+      <c r="E119" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F119" s="42" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A120" s="40" t="s">
+        <v>594</v>
+      </c>
+      <c r="B120" s="40" t="s">
+        <v>599</v>
+      </c>
+      <c r="C120" s="41" t="s">
+        <v>533</v>
+      </c>
+      <c r="D120" s="42" t="s">
+        <v>534</v>
+      </c>
+      <c r="E120" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F120" s="42"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="42"/>
+      <c r="B121" s="42"/>
+      <c r="C121" s="45"/>
+      <c r="D121" s="42" t="s">
+        <v>535</v>
+      </c>
+      <c r="E121" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F121" s="42"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="42"/>
+      <c r="B122" s="42"/>
+      <c r="C122" s="41" t="s">
+        <v>536</v>
+      </c>
+      <c r="D122" s="42" t="s">
+        <v>537</v>
+      </c>
+      <c r="E122" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F122" s="42" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="42"/>
+      <c r="B123" s="42"/>
+      <c r="C123" s="44"/>
+      <c r="D123" s="42" t="s">
+        <v>539</v>
+      </c>
+      <c r="E123" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F123" s="42" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="42"/>
+      <c r="B124" s="42"/>
+      <c r="C124" s="45"/>
+      <c r="D124" s="42" t="s">
+        <v>541</v>
+      </c>
+      <c r="E124" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F124" s="42" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="42"/>
+      <c r="B125" s="42"/>
+      <c r="C125" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="D125" s="42" t="s">
+        <v>544</v>
+      </c>
+      <c r="E125" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F125" s="42" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="42"/>
+      <c r="B126" s="42"/>
+      <c r="C126" s="44"/>
+      <c r="D126" s="42" t="s">
+        <v>546</v>
+      </c>
+      <c r="E126" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F126" s="42" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="42"/>
+      <c r="B127" s="42"/>
+      <c r="C127" s="45"/>
+      <c r="D127" s="42" t="s">
+        <v>548</v>
+      </c>
+      <c r="E127" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F127" s="42" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="42"/>
+      <c r="B128" s="40" t="s">
+        <v>600</v>
+      </c>
+      <c r="C128" s="41" t="s">
+        <v>550</v>
+      </c>
+      <c r="D128" s="42" t="s">
+        <v>551</v>
+      </c>
+      <c r="E128" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F128" s="42" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="42"/>
+      <c r="B129" s="42"/>
+      <c r="C129" s="44"/>
+      <c r="D129" s="42" t="s">
+        <v>553</v>
+      </c>
+      <c r="E129" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F129" s="42" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="42"/>
+      <c r="B130" s="42"/>
+      <c r="C130" s="45"/>
+      <c r="D130" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="E130" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F130" s="42" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="42"/>
+      <c r="B131" s="42"/>
+      <c r="C131" s="41" t="s">
+        <v>557</v>
+      </c>
+      <c r="D131" s="42" t="s">
+        <v>558</v>
+      </c>
+      <c r="E131" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F131" s="42" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="42"/>
+      <c r="B132" s="42"/>
+      <c r="C132" s="44"/>
+      <c r="D132" s="42" t="s">
+        <v>560</v>
+      </c>
+      <c r="E132" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F132" s="42" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="42"/>
+      <c r="B133" s="42"/>
+      <c r="C133" s="44"/>
+      <c r="D133" s="42" t="s">
+        <v>562</v>
+      </c>
+      <c r="E133" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F133" s="42" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="42"/>
+      <c r="B134" s="42"/>
+      <c r="C134" s="45"/>
+      <c r="D134" s="42" t="s">
+        <v>564</v>
+      </c>
+      <c r="E134" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F134" s="42" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="42"/>
+      <c r="B135" s="42"/>
+      <c r="C135" s="41" t="s">
+        <v>566</v>
+      </c>
+      <c r="D135" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="E135" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F135" s="42" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="42"/>
+      <c r="B136" s="42"/>
+      <c r="C136" s="44"/>
+      <c r="D136" s="42" t="s">
+        <v>569</v>
+      </c>
+      <c r="E136" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F136" s="42" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="42"/>
+      <c r="B137" s="42"/>
+      <c r="C137" s="44"/>
+      <c r="D137" s="42" t="s">
+        <v>570</v>
+      </c>
+      <c r="E137" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F137" s="42" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="42"/>
+      <c r="B138" s="42"/>
+      <c r="C138" s="45"/>
+      <c r="D138" s="42" t="s">
+        <v>572</v>
+      </c>
+      <c r="E138" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F138" s="42" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="42"/>
+      <c r="B139" s="42"/>
+      <c r="C139" s="41" t="s">
+        <v>573</v>
+      </c>
+      <c r="D139" s="42" t="s">
+        <v>574</v>
+      </c>
+      <c r="E139" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F139" s="42" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="42"/>
+      <c r="B140" s="42"/>
+      <c r="C140" s="44"/>
+      <c r="D140" s="42" t="s">
+        <v>576</v>
+      </c>
+      <c r="E140" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F140" s="42" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="42"/>
+      <c r="B141" s="42"/>
+      <c r="C141" s="44"/>
+      <c r="D141" s="42" t="s">
+        <v>578</v>
+      </c>
+      <c r="E141" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F141" s="42" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="42"/>
+      <c r="B142" s="42"/>
+      <c r="C142" s="44"/>
+      <c r="D142" s="42" t="s">
+        <v>580</v>
+      </c>
+      <c r="E142" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F142" s="42" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="42"/>
+      <c r="B143" s="42"/>
+      <c r="C143" s="45"/>
+      <c r="D143" s="42" t="s">
+        <v>582</v>
+      </c>
+      <c r="E143" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F143" s="42" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="42"/>
+      <c r="B144" s="42"/>
+      <c r="C144" s="41" t="s">
+        <v>584</v>
+      </c>
+      <c r="D144" s="42" t="s">
+        <v>585</v>
+      </c>
+      <c r="E144" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F144" s="42" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="42"/>
+      <c r="B145" s="42"/>
+      <c r="C145" s="44"/>
+      <c r="D145" s="42" t="s">
+        <v>587</v>
+      </c>
+      <c r="E145" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F145" s="42" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="42"/>
+      <c r="B146" s="42"/>
+      <c r="C146" s="44"/>
+      <c r="D146" s="42" t="s">
+        <v>589</v>
+      </c>
+      <c r="E146" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F146" s="42" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="42"/>
+      <c r="B147" s="42"/>
+      <c r="C147" s="45"/>
+      <c r="D147" s="42" t="s">
+        <v>591</v>
+      </c>
+      <c r="E147" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F147" s="42" t="s">
+        <v>592</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="36">
+    <mergeCell ref="C135:C138"/>
+    <mergeCell ref="C139:C143"/>
+    <mergeCell ref="C144:C147"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="C122:C124"/>
+    <mergeCell ref="C125:C127"/>
+    <mergeCell ref="C128:C130"/>
+    <mergeCell ref="C131:C134"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="C117:C119"/>
+    <mergeCell ref="C86:C94"/>
+    <mergeCell ref="C95:C101"/>
+    <mergeCell ref="C102:C104"/>
+    <mergeCell ref="C105:C108"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="C9:C21"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="C57:C62"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C66:C71"/>
     <mergeCell ref="C81:C82"/>
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="C37:C39"/>
@@ -6430,16 +7397,6 @@
     <mergeCell ref="C48:C54"/>
     <mergeCell ref="C55:C56"/>
     <mergeCell ref="C72:C80"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="C57:C62"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="C66:C71"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="C9:C21"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="C26:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -6487,47 +7444,47 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
+      <c r="A6" s="12">
         <f>COUNTIF(F9:F52, "Passed")</f>
         <v>37</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="13">
         <f>COUNTIF(F9:F52, "Failed")</f>
         <v>5</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="14">
         <f>COUNTBLANK(F9:F52) + COUNTIF(F9:F52, "Untested")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="15">
         <f>COUNTIF(F9:F52, "Blocked")</f>
         <v>2</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="16">
         <f>COUNTIF(F9:F52, "Skipped")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="16">
         <f>COUNTA(A9:A52)</f>
         <v>44</v>
       </c>
@@ -6577,7 +7534,7 @@
       <c r="F9" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="21">
         <v>46323</v>
       </c>
       <c r="H9" s="9"/>
@@ -6601,7 +7558,7 @@
       <c r="F10" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="21">
         <v>46324</v>
       </c>
       <c r="H10" s="9"/>
@@ -6625,7 +7582,7 @@
       <c r="F11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="21">
         <v>46325</v>
       </c>
       <c r="H11" s="9"/>
@@ -6649,7 +7606,7 @@
       <c r="F12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="21">
         <v>46326</v>
       </c>
       <c r="H12" s="9"/>
@@ -6673,11 +7630,11 @@
       <c r="F13" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="21">
         <v>46327</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
@@ -6699,7 +7656,7 @@
       <c r="F14" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="21">
         <v>46328</v>
       </c>
       <c r="H14" s="9"/>
@@ -6723,7 +7680,7 @@
       <c r="F15" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="21">
         <v>46329</v>
       </c>
       <c r="H15" s="9"/>
@@ -6747,7 +7704,7 @@
       <c r="F16" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="21">
         <v>46330</v>
       </c>
       <c r="H16" s="9"/>
@@ -6771,7 +7728,7 @@
       <c r="F17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="21">
         <v>46331</v>
       </c>
       <c r="H17" s="9"/>
@@ -6795,7 +7752,7 @@
       <c r="F18" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="21">
         <v>46332</v>
       </c>
       <c r="H18" s="9"/>
@@ -6819,7 +7776,7 @@
       <c r="F19" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="21">
         <v>46333</v>
       </c>
       <c r="H19" s="9"/>
@@ -6843,7 +7800,7 @@
       <c r="F20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="21">
         <v>46334</v>
       </c>
       <c r="H20" s="9"/>
@@ -6867,7 +7824,7 @@
       <c r="F21" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="21">
         <v>46335</v>
       </c>
       <c r="H21" s="9"/>
@@ -6891,7 +7848,7 @@
       <c r="F22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="21">
         <v>46336</v>
       </c>
       <c r="H22" s="9"/>
@@ -6915,7 +7872,7 @@
       <c r="F23" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="21">
         <v>46337</v>
       </c>
       <c r="H23" s="9"/>
@@ -6939,7 +7896,7 @@
       <c r="F24" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="21">
         <v>46338</v>
       </c>
       <c r="H24" s="9"/>
@@ -6963,7 +7920,7 @@
       <c r="F25" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="21">
         <v>46339</v>
       </c>
       <c r="H25" s="9"/>
@@ -6987,7 +7944,7 @@
       <c r="F26" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="21">
         <v>46340</v>
       </c>
       <c r="H26" s="9"/>
@@ -7011,7 +7968,7 @@
       <c r="F27" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="21">
         <v>46341</v>
       </c>
       <c r="H27" s="9"/>
@@ -7035,7 +7992,7 @@
       <c r="F28" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="21">
         <v>46342</v>
       </c>
       <c r="H28" s="9"/>
@@ -7059,7 +8016,7 @@
       <c r="F29" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="21">
         <v>46343</v>
       </c>
       <c r="H29" s="9"/>
@@ -7083,11 +8040,11 @@
       <c r="F30" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="21">
         <v>46344</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
@@ -7109,7 +8066,7 @@
       <c r="F31" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="21">
         <v>46345</v>
       </c>
       <c r="H31" s="9"/>
@@ -7133,7 +8090,7 @@
       <c r="F32" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="21">
         <v>46346</v>
       </c>
       <c r="H32" s="9"/>
@@ -7157,11 +8114,11 @@
       <c r="F33" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G33" s="27">
+      <c r="G33" s="21">
         <v>46347</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
@@ -7183,11 +8140,11 @@
       <c r="F34" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G34" s="27">
+      <c r="G34" s="21">
         <v>46348</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
@@ -7209,7 +8166,7 @@
       <c r="F35" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G35" s="27">
+      <c r="G35" s="21">
         <v>46349</v>
       </c>
       <c r="H35" s="9"/>
@@ -7233,7 +8190,7 @@
       <c r="F36" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G36" s="27">
+      <c r="G36" s="21">
         <v>46350</v>
       </c>
       <c r="H36" s="9"/>
@@ -7257,7 +8214,7 @@
       <c r="F37" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G37" s="27">
+      <c r="G37" s="21">
         <v>46351</v>
       </c>
       <c r="H37" s="9"/>
@@ -7281,11 +8238,11 @@
       <c r="F38" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="21">
         <v>46352</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
@@ -7307,11 +8264,11 @@
       <c r="F39" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G39" s="27">
+      <c r="G39" s="21">
         <v>46353</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
@@ -7333,7 +8290,7 @@
       <c r="F40" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G40" s="27">
+      <c r="G40" s="21">
         <v>46354</v>
       </c>
       <c r="H40" s="9"/>
@@ -7357,7 +8314,7 @@
       <c r="F41" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G41" s="27">
+      <c r="G41" s="21">
         <v>46355</v>
       </c>
       <c r="H41" s="9"/>
@@ -7381,7 +8338,7 @@
       <c r="F42" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G42" s="27">
+      <c r="G42" s="21">
         <v>46356</v>
       </c>
       <c r="H42" s="9"/>
@@ -7405,7 +8362,7 @@
       <c r="F43" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G43" s="27">
+      <c r="G43" s="21">
         <v>46357</v>
       </c>
       <c r="H43" s="9"/>
@@ -7429,7 +8386,7 @@
       <c r="F44" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G44" s="27">
+      <c r="G44" s="21">
         <v>46358</v>
       </c>
       <c r="H44" s="9"/>
@@ -7453,7 +8410,7 @@
       <c r="F45" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G45" s="27">
+      <c r="G45" s="21">
         <v>46359</v>
       </c>
       <c r="H45" s="9"/>
@@ -7477,7 +8434,7 @@
       <c r="F46" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G46" s="27">
+      <c r="G46" s="21">
         <v>46360</v>
       </c>
       <c r="H46" s="9"/>
@@ -7501,7 +8458,7 @@
       <c r="F47" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G47" s="27">
+      <c r="G47" s="21">
         <v>46361</v>
       </c>
       <c r="H47" s="9"/>
@@ -7525,7 +8482,7 @@
       <c r="F48" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G48" s="27">
+      <c r="G48" s="21">
         <v>46362</v>
       </c>
       <c r="H48" s="9"/>
@@ -7549,7 +8506,7 @@
       <c r="F49" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G49" s="27">
+      <c r="G49" s="21">
         <v>46363</v>
       </c>
       <c r="H49" s="9"/>
@@ -7573,7 +8530,7 @@
       <c r="F50" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G50" s="27">
+      <c r="G50" s="21">
         <v>46364</v>
       </c>
       <c r="H50" s="9"/>
@@ -7597,11 +8554,11 @@
       <c r="F51" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G51" s="27">
+      <c r="G51" s="21">
         <v>46365</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="165.6" x14ac:dyDescent="0.3">
@@ -7623,11 +8580,11 @@
       <c r="F52" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G52" s="27">
+      <c r="G52" s="21">
         <v>46366</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -7676,47 +8633,47 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
+      <c r="A6" s="12">
         <f>COUNTIF(F9:F28, "Passed")</f>
         <v>18</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="13">
         <f>COUNTIF(F9:F28, "Failed")</f>
         <v>2</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="14">
         <f>COUNTBLANK(F9:F28) + COUNTIF(F9:F28, "Untested")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="15">
         <f>COUNTIF(F9:F28, "Blocked")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="16">
         <f>COUNTIF(F9:F28, "Skipped")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="16">
         <f>COUNTA(A9:A28)</f>
         <v>20</v>
       </c>
@@ -7766,7 +8723,7 @@
       <c r="F9" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="21">
         <v>46323</v>
       </c>
       <c r="H9" s="9"/>
@@ -7790,7 +8747,7 @@
       <c r="F10" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="21">
         <v>46323</v>
       </c>
       <c r="H10" s="9"/>
@@ -7814,7 +8771,7 @@
       <c r="F11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="21">
         <v>46323</v>
       </c>
       <c r="H11" s="9"/>
@@ -7838,7 +8795,7 @@
       <c r="F12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="21">
         <v>46323</v>
       </c>
       <c r="H12" s="9"/>
@@ -7848,10 +8805,10 @@
         <v>313</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>317</v>
@@ -7862,7 +8819,7 @@
       <c r="F13" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="21">
         <v>46323</v>
       </c>
       <c r="H13" s="9"/>
@@ -7886,7 +8843,7 @@
       <c r="F14" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="21">
         <v>46323</v>
       </c>
       <c r="H14" s="9"/>
@@ -7910,11 +8867,11 @@
       <c r="F15" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="21">
         <v>46323</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
@@ -7936,7 +8893,7 @@
       <c r="F16" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="21">
         <v>46323</v>
       </c>
       <c r="H16" s="9"/>
@@ -7960,7 +8917,7 @@
       <c r="F17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="21">
         <v>46323</v>
       </c>
       <c r="H17" s="9"/>
@@ -7984,7 +8941,7 @@
       <c r="F18" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="21">
         <v>46323</v>
       </c>
       <c r="H18" s="9"/>
@@ -8008,7 +8965,7 @@
       <c r="F19" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="21">
         <v>46323</v>
       </c>
       <c r="H19" s="9"/>
@@ -8032,7 +8989,7 @@
       <c r="F20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="21">
         <v>46323</v>
       </c>
       <c r="H20" s="9"/>
@@ -8056,7 +9013,7 @@
       <c r="F21" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="21">
         <v>46323</v>
       </c>
       <c r="H21" s="9"/>
@@ -8080,7 +9037,7 @@
       <c r="F22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="21">
         <v>46323</v>
       </c>
       <c r="H22" s="9"/>
@@ -8104,7 +9061,7 @@
       <c r="F23" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="21">
         <v>46323</v>
       </c>
       <c r="H23" s="9"/>
@@ -8128,11 +9085,11 @@
       <c r="F24" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="21">
         <v>46323</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
@@ -8154,7 +9111,7 @@
       <c r="F25" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="21">
         <v>46323</v>
       </c>
       <c r="H25" s="9"/>
@@ -8178,7 +9135,7 @@
       <c r="F26" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="21">
         <v>46323</v>
       </c>
       <c r="H26" s="9"/>
@@ -8202,7 +9159,7 @@
       <c r="F27" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="21">
         <v>46323</v>
       </c>
       <c r="H27" s="9"/>
@@ -8226,7 +9183,7 @@
       <c r="F28" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="21">
         <v>46323</v>
       </c>
       <c r="H28" s="9"/>
@@ -8260,7 +9217,7 @@
       <c r="B2" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="17" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8281,47 +9238,47 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
+      <c r="A6" s="12">
         <f>COUNTIF(F9:F28, "Passed")</f>
         <v>16</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="13">
         <f>COUNTIF(F9:F28, "Failed")</f>
         <v>4</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="14">
         <f>COUNTBLANK(F9:F28) + COUNTIF(F9:F28, "Untested")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="15">
         <f>COUNTIF(F9:F28, "Blocked")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="16">
         <f>COUNTIF(F9:F28, "Skipped")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="16">
         <f>COUNTA(A9:A28)</f>
         <v>20</v>
       </c>
@@ -8371,7 +9328,7 @@
       <c r="F9" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="21">
         <v>46324</v>
       </c>
       <c r="H9" s="9"/>
@@ -8395,7 +9352,7 @@
       <c r="F10" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="21">
         <v>46324</v>
       </c>
       <c r="H10" s="9"/>
@@ -8419,7 +9376,7 @@
       <c r="F11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="21">
         <v>46324</v>
       </c>
       <c r="H11" s="9"/>
@@ -8443,7 +9400,7 @@
       <c r="F12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="21">
         <v>46324</v>
       </c>
       <c r="H12" s="9"/>
@@ -8467,7 +9424,7 @@
       <c r="F13" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="21">
         <v>46324</v>
       </c>
       <c r="H13" s="9"/>
@@ -8491,7 +9448,7 @@
       <c r="F14" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="21">
         <v>46324</v>
       </c>
       <c r="H14" s="9"/>
@@ -8515,7 +9472,7 @@
       <c r="F15" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="21">
         <v>46324</v>
       </c>
       <c r="H15" s="9"/>
@@ -8539,7 +9496,7 @@
       <c r="F16" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="21">
         <v>46324</v>
       </c>
       <c r="H16" s="9"/>
@@ -8563,7 +9520,7 @@
       <c r="F17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="21">
         <v>46324</v>
       </c>
       <c r="H17" s="9"/>
@@ -8587,11 +9544,11 @@
       <c r="F18" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="21">
         <v>46324</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
@@ -8613,11 +9570,11 @@
       <c r="F19" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="21">
         <v>46324</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
@@ -8639,11 +9596,11 @@
       <c r="F20" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="21">
         <v>46324</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
@@ -8665,11 +9622,11 @@
       <c r="F21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="21">
         <v>46324</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
@@ -8691,7 +9648,7 @@
       <c r="F22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="21">
         <v>46324</v>
       </c>
       <c r="H22" s="9"/>
@@ -8715,7 +9672,7 @@
       <c r="F23" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="21">
         <v>46324</v>
       </c>
       <c r="H23" s="9"/>
@@ -8739,7 +9696,7 @@
       <c r="F24" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="21">
         <v>46324</v>
       </c>
       <c r="H24" s="9"/>
@@ -8763,7 +9720,7 @@
       <c r="F25" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="21">
         <v>46324</v>
       </c>
       <c r="H25" s="9"/>
@@ -8787,7 +9744,7 @@
       <c r="F26" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="21">
         <v>46324</v>
       </c>
       <c r="H26" s="9"/>
@@ -8811,7 +9768,7 @@
       <c r="F27" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="21">
         <v>46324</v>
       </c>
       <c r="H27" s="9"/>
@@ -8835,7 +9792,7 @@
       <c r="F28" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="21">
         <v>46324</v>
       </c>
       <c r="H28" s="9"/>
@@ -8847,6 +9804,642 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824D3F37-C310-4517-B541-4114832CA285}">
+  <dimension ref="A2:H34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" style="52" customWidth="1"/>
+    <col min="2" max="2" width="38" style="52" customWidth="1"/>
+    <col min="3" max="4" width="45" style="52" customWidth="1"/>
+    <col min="5" max="5" width="28" style="52" customWidth="1"/>
+    <col min="6" max="6" width="12" style="52" customWidth="1"/>
+    <col min="7" max="7" width="14" style="52" customWidth="1"/>
+    <col min="8" max="8" width="35" style="52" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="52"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.35">
+      <c r="A2" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.35">
+      <c r="A3" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.35">
+      <c r="A4" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.3">
+      <c r="A5" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="54">
+        <f>COUNTIF(F9:F34, "Passed")</f>
+        <v>0</v>
+      </c>
+      <c r="B6" s="55">
+        <f>COUNTIF(F9:F34, "Failed")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="56">
+        <f>COUNTBLANK(F9:F34) + COUNTIF(F9:F34, "Untested")</f>
+        <v>26</v>
+      </c>
+      <c r="D6" s="57">
+        <f>COUNTIF(F9:F34, "Blocked")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="58">
+        <f>COUNTIF(F9:F34, "Skipped")</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="58">
+        <f>COUNTA(A9:A34)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="59" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="90" x14ac:dyDescent="0.3">
+      <c r="A9" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>614</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>615</v>
+      </c>
+      <c r="D9" s="61" t="s">
+        <v>616</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="61"/>
+    </row>
+    <row r="10" spans="1:8" ht="90" x14ac:dyDescent="0.3">
+      <c r="A10" s="60" t="s">
+        <v>617</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>618</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>619</v>
+      </c>
+      <c r="D10" s="61" t="s">
+        <v>620</v>
+      </c>
+      <c r="E10" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="61"/>
+    </row>
+    <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.3">
+      <c r="A11" s="60" t="s">
+        <v>621</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>623</v>
+      </c>
+      <c r="D11" s="61" t="s">
+        <v>624</v>
+      </c>
+      <c r="E11" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="61"/>
+    </row>
+    <row r="12" spans="1:8" ht="105" x14ac:dyDescent="0.3">
+      <c r="A12" s="60" t="s">
+        <v>625</v>
+      </c>
+      <c r="B12" s="61" t="s">
+        <v>626</v>
+      </c>
+      <c r="C12" s="61" t="s">
+        <v>627</v>
+      </c>
+      <c r="D12" s="61" t="s">
+        <v>628</v>
+      </c>
+      <c r="E12" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="61"/>
+    </row>
+    <row r="13" spans="1:8" ht="105" x14ac:dyDescent="0.3">
+      <c r="A13" s="60" t="s">
+        <v>629</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>630</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>631</v>
+      </c>
+      <c r="D13" s="61" t="s">
+        <v>632</v>
+      </c>
+      <c r="E13" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="61"/>
+    </row>
+    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.3">
+      <c r="A14" s="60" t="s">
+        <v>633</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>490</v>
+      </c>
+      <c r="C14" s="61" t="s">
+        <v>634</v>
+      </c>
+      <c r="D14" s="61" t="s">
+        <v>635</v>
+      </c>
+      <c r="E14" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="61"/>
+    </row>
+    <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.3">
+      <c r="A15" s="60" t="s">
+        <v>636</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>637</v>
+      </c>
+      <c r="C15" s="61" t="s">
+        <v>623</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>638</v>
+      </c>
+      <c r="E15" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
+    </row>
+    <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.3">
+      <c r="A16" s="60" t="s">
+        <v>639</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>494</v>
+      </c>
+      <c r="C16" s="61" t="s">
+        <v>640</v>
+      </c>
+      <c r="D16" s="61" t="s">
+        <v>641</v>
+      </c>
+      <c r="E16" s="60" t="s">
+        <v>636</v>
+      </c>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="61"/>
+    </row>
+    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.3">
+      <c r="A17" s="60" t="s">
+        <v>642</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>643</v>
+      </c>
+      <c r="C17" s="61" t="s">
+        <v>644</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>645</v>
+      </c>
+      <c r="E17" s="60" t="s">
+        <v>636</v>
+      </c>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="61"/>
+    </row>
+    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.3">
+      <c r="A18" s="60" t="s">
+        <v>646</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>496</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>647</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>648</v>
+      </c>
+      <c r="E18" s="60" t="s">
+        <v>642</v>
+      </c>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="61"/>
+    </row>
+    <row r="19" spans="1:8" ht="60" x14ac:dyDescent="0.3">
+      <c r="A19" s="60" t="s">
+        <v>649</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>497</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>650</v>
+      </c>
+      <c r="D19" s="61" t="s">
+        <v>651</v>
+      </c>
+      <c r="E19" s="60" t="s">
+        <v>646</v>
+      </c>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="61"/>
+    </row>
+    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.3">
+      <c r="A20" s="60" t="s">
+        <v>652</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>653</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>654</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>655</v>
+      </c>
+      <c r="E20" s="60" t="s">
+        <v>642</v>
+      </c>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="61"/>
+    </row>
+    <row r="21" spans="1:8" ht="60" x14ac:dyDescent="0.3">
+      <c r="A21" s="60" t="s">
+        <v>656</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>657</v>
+      </c>
+      <c r="C21" s="61" t="s">
+        <v>658</v>
+      </c>
+      <c r="D21" s="61" t="s">
+        <v>659</v>
+      </c>
+      <c r="E21" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="61"/>
+    </row>
+    <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.3">
+      <c r="A22" s="60" t="s">
+        <v>660</v>
+      </c>
+      <c r="B22" s="61" t="s">
+        <v>661</v>
+      </c>
+      <c r="C22" s="61" t="s">
+        <v>662</v>
+      </c>
+      <c r="D22" s="61" t="s">
+        <v>663</v>
+      </c>
+      <c r="E22" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="61"/>
+    </row>
+    <row r="23" spans="1:8" ht="60" x14ac:dyDescent="0.3">
+      <c r="A23" s="60" t="s">
+        <v>664</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>665</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>666</v>
+      </c>
+      <c r="D23" s="61" t="s">
+        <v>667</v>
+      </c>
+      <c r="E23" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="61"/>
+    </row>
+    <row r="24" spans="1:8" ht="45" x14ac:dyDescent="0.3">
+      <c r="A24" s="60" t="s">
+        <v>668</v>
+      </c>
+      <c r="B24" s="61" t="s">
+        <v>504</v>
+      </c>
+      <c r="C24" s="61" t="s">
+        <v>669</v>
+      </c>
+      <c r="D24" s="61" t="s">
+        <v>670</v>
+      </c>
+      <c r="E24" s="60" t="s">
+        <v>660</v>
+      </c>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="61"/>
+    </row>
+    <row r="25" spans="1:8" ht="60" x14ac:dyDescent="0.3">
+      <c r="A25" s="60" t="s">
+        <v>671</v>
+      </c>
+      <c r="B25" s="61" t="s">
+        <v>506</v>
+      </c>
+      <c r="C25" s="61" t="s">
+        <v>672</v>
+      </c>
+      <c r="D25" s="61" t="s">
+        <v>673</v>
+      </c>
+      <c r="E25" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="61"/>
+    </row>
+    <row r="26" spans="1:8" ht="60" x14ac:dyDescent="0.3">
+      <c r="A26" s="60" t="s">
+        <v>674</v>
+      </c>
+      <c r="B26" s="61" t="s">
+        <v>508</v>
+      </c>
+      <c r="C26" s="61" t="s">
+        <v>675</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>676</v>
+      </c>
+      <c r="E26" s="60" t="s">
+        <v>668</v>
+      </c>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="61"/>
+    </row>
+    <row r="27" spans="1:8" ht="105" x14ac:dyDescent="0.3">
+      <c r="A27" s="60" t="s">
+        <v>677</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>510</v>
+      </c>
+      <c r="C27" s="61" t="s">
+        <v>678</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>679</v>
+      </c>
+      <c r="E27" s="60" t="s">
+        <v>664</v>
+      </c>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="61"/>
+    </row>
+    <row r="28" spans="1:8" ht="60" x14ac:dyDescent="0.3">
+      <c r="A28" s="60" t="s">
+        <v>680</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>513</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>681</v>
+      </c>
+      <c r="D28" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="E28" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F28" s="60"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="61"/>
+    </row>
+    <row r="29" spans="1:8" ht="90" x14ac:dyDescent="0.3">
+      <c r="A29" s="60" t="s">
+        <v>683</v>
+      </c>
+      <c r="B29" s="61" t="s">
+        <v>515</v>
+      </c>
+      <c r="C29" s="61" t="s">
+        <v>684</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>685</v>
+      </c>
+      <c r="E29" s="60" t="s">
+        <v>680</v>
+      </c>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="61"/>
+    </row>
+    <row r="30" spans="1:8" ht="105" x14ac:dyDescent="0.3">
+      <c r="A30" s="60" t="s">
+        <v>686</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>518</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>687</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>688</v>
+      </c>
+      <c r="E30" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="61"/>
+    </row>
+    <row r="31" spans="1:8" ht="90" x14ac:dyDescent="0.3">
+      <c r="A31" s="60" t="s">
+        <v>689</v>
+      </c>
+      <c r="B31" s="61" t="s">
+        <v>519</v>
+      </c>
+      <c r="C31" s="61" t="s">
+        <v>690</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>691</v>
+      </c>
+      <c r="E31" s="60" t="s">
+        <v>686</v>
+      </c>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="61"/>
+    </row>
+    <row r="32" spans="1:8" ht="90" x14ac:dyDescent="0.3">
+      <c r="A32" s="60" t="s">
+        <v>692</v>
+      </c>
+      <c r="B32" s="61" t="s">
+        <v>522</v>
+      </c>
+      <c r="C32" s="61" t="s">
+        <v>693</v>
+      </c>
+      <c r="D32" s="61" t="s">
+        <v>694</v>
+      </c>
+      <c r="E32" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="61"/>
+    </row>
+    <row r="33" spans="1:8" ht="45" x14ac:dyDescent="0.3">
+      <c r="A33" s="60" t="s">
+        <v>695</v>
+      </c>
+      <c r="B33" s="61" t="s">
+        <v>526</v>
+      </c>
+      <c r="C33" s="61" t="s">
+        <v>696</v>
+      </c>
+      <c r="D33" s="61" t="s">
+        <v>697</v>
+      </c>
+      <c r="E33" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="61"/>
+    </row>
+    <row r="34" spans="1:8" ht="60" x14ac:dyDescent="0.3">
+      <c r="A34" s="60" t="s">
+        <v>698</v>
+      </c>
+      <c r="B34" s="61" t="s">
+        <v>531</v>
+      </c>
+      <c r="C34" s="61" t="s">
+        <v>699</v>
+      </c>
+      <c r="D34" s="61" t="s">
+        <v>700</v>
+      </c>
+      <c r="E34" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="61"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:I1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8860,16 +10453,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="22" t="s">
         <v>450</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="4" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -8903,22 +10496,22 @@
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>451</v>
+      <c r="C6" s="49" t="s">
+        <v>609</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>13</v>
+      <c r="G6" s="48">
+        <v>46324</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>16</v>
@@ -8932,13 +10525,13 @@
         <v>27</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>455</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>456</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>61</v>
@@ -8950,7 +10543,7 @@
         <v>64</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -9050,56 +10643,56 @@
       </c>
     </row>
     <row r="14" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="D14" s="11">
+        <f>SUM(D11:D13)</f>
+        <v>71</v>
+      </c>
+      <c r="E14" s="11">
+        <f>SUM(E11:E13)</f>
+        <v>11</v>
+      </c>
+      <c r="F14" s="11">
+        <f>SUM(F11:F13)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="11">
+        <f>SUM(G11:G13)</f>
+        <v>2</v>
+      </c>
+      <c r="H14" s="11">
+        <f>SUM(H11:H13)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="11">
+        <f>SUM(I11:I13)</f>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C16" s="19" t="s">
         <v>458</v>
       </c>
-      <c r="D14" s="13">
-        <f t="shared" ref="D14:I14" si="0">SUM(D11:D13)</f>
-        <v>71</v>
-      </c>
-      <c r="E14" s="13">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="F14" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="13">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H14" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="13">
-        <f t="shared" si="0"/>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C16" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="E16" s="26">
+      <c r="E16" s="20">
         <f>IF(I14-H14=0, 0, (D14+E14)/(I14-H14)*100)</f>
         <v>97.61904761904762</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C17" s="19" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="17" spans="3:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C17" s="25" t="s">
-        <v>461</v>
-      </c>
-      <c r="E17" s="26">
+      <c r="E17" s="20">
         <f>IF(D14+E14=0, 0, D14/(D14+E14)*100)</f>
         <v>86.58536585365853</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="21" spans="3:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
